--- a/research/traditional_assets/database/data/greece/greece_steel.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_steel.xlsx
@@ -1909,7 +1909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2046,22 +2046,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1211125356863122</v>
+        <v>0.1208811881078023</v>
       </c>
       <c r="C2">
-        <v>35.49179569482366</v>
+        <v>35.23383075980561</v>
       </c>
       <c r="D2">
-        <v>31.36179569482366</v>
+        <v>31.4584307598056</v>
       </c>
       <c r="E2">
-        <v>-25.9</v>
+        <v>-25.5454</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3546</v>
       </c>
       <c r="G2">
         <v>4.13</v>
@@ -2082,28 +2082,28 @@
         <v>1.288</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01783638</v>
       </c>
       <c r="N2">
-        <v>1.288</v>
+        <v>1.27016362</v>
       </c>
       <c r="O2">
-        <v>0.2833599999999999</v>
+        <v>0.2794359963999999</v>
       </c>
       <c r="P2">
-        <v>1.00464</v>
+        <v>0.9907276235999998</v>
       </c>
       <c r="Q2">
-        <v>1.35264</v>
+        <v>1.3387276236</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1211125356863122</v>
+        <v>0.1217059071795983</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.989308430033778</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>72.21196229279707</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2128,22 +2128,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1208811881078023</v>
+        <v>0.1206498405292925</v>
       </c>
       <c r="C3">
-        <v>35.23383075980561</v>
+        <v>34.97646318847261</v>
       </c>
       <c r="D3">
-        <v>31.4584307598056</v>
+        <v>31.55566318847261</v>
       </c>
       <c r="E3">
-        <v>-25.5454</v>
+        <v>-25.1908</v>
       </c>
       <c r="F3">
-        <v>0.3546</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="G3">
         <v>4.13</v>
@@ -2164,28 +2164,28 @@
         <v>1.288</v>
       </c>
       <c r="M3">
-        <v>0.01783638</v>
+        <v>0.03567276</v>
       </c>
       <c r="N3">
-        <v>1.27016362</v>
+        <v>1.25232724</v>
       </c>
       <c r="O3">
-        <v>0.2794359963999999</v>
+        <v>0.2755119928</v>
       </c>
       <c r="P3">
-        <v>0.9907276235999998</v>
+        <v>0.9768152471999998</v>
       </c>
       <c r="Q3">
-        <v>1.3387276236</v>
+        <v>1.3248152472</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1217059071795983</v>
+        <v>0.1223113882951964</v>
       </c>
       <c r="T3">
-        <v>0.989308430033778</v>
+        <v>0.9971998787252497</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>72.21196229279707</v>
+        <v>36.10598114639854</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2210,22 +2210,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1206498405292925</v>
+        <v>0.1204184929507826</v>
       </c>
       <c r="C4">
-        <v>34.97646318847261</v>
+        <v>34.71969853703349</v>
       </c>
       <c r="D4">
-        <v>31.55566318847261</v>
+        <v>31.65349853703349</v>
       </c>
       <c r="E4">
-        <v>-25.1908</v>
+        <v>-24.8362</v>
       </c>
       <c r="F4">
-        <v>0.7092000000000001</v>
+        <v>1.0638</v>
       </c>
       <c r="G4">
         <v>4.13</v>
@@ -2246,28 +2246,28 @@
         <v>1.288</v>
       </c>
       <c r="M4">
-        <v>0.03567276</v>
+        <v>0.05350914</v>
       </c>
       <c r="N4">
-        <v>1.25232724</v>
+        <v>1.23449086</v>
       </c>
       <c r="O4">
-        <v>0.2755119928</v>
+        <v>0.2715879891999999</v>
       </c>
       <c r="P4">
-        <v>0.9768152471999998</v>
+        <v>0.9629028707999998</v>
       </c>
       <c r="Q4">
-        <v>1.3248152472</v>
+        <v>1.3109028708</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1223113882951964</v>
+        <v>0.1229293535575078</v>
       </c>
       <c r="T4">
-        <v>0.9971998787252497</v>
+        <v>1.00525403769902</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>36.10598114639854</v>
+        <v>24.07065409759902</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2292,22 +2292,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1204184929507826</v>
+        <v>0.1201871453722727</v>
       </c>
       <c r="C5">
-        <v>34.71969853703349</v>
+        <v>34.4635424308173</v>
       </c>
       <c r="D5">
-        <v>31.65349853703349</v>
+        <v>31.75194243081729</v>
       </c>
       <c r="E5">
-        <v>-24.8362</v>
+        <v>-24.4816</v>
       </c>
       <c r="F5">
-        <v>1.0638</v>
+        <v>1.4184</v>
       </c>
       <c r="G5">
         <v>4.13</v>
@@ -2328,28 +2328,28 @@
         <v>1.288</v>
       </c>
       <c r="M5">
-        <v>0.05350914</v>
+        <v>0.07134552</v>
       </c>
       <c r="N5">
-        <v>1.23449086</v>
+        <v>1.21665448</v>
       </c>
       <c r="O5">
-        <v>0.2715879891999999</v>
+        <v>0.2676639856</v>
       </c>
       <c r="P5">
-        <v>0.9629028707999998</v>
+        <v>0.9489904943999998</v>
       </c>
       <c r="Q5">
-        <v>1.3109028708</v>
+        <v>1.2969904944</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1229293535575078</v>
+        <v>0.1235601930961174</v>
       </c>
       <c r="T5">
-        <v>1.00525403769902</v>
+        <v>1.01347599165141</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>24.07065409759902</v>
+        <v>18.05299057319927</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2374,22 +2374,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1201871453722727</v>
+        <v>0.1199557977937628</v>
       </c>
       <c r="C6">
-        <v>34.4635424308173</v>
+        <v>34.20800056535162</v>
       </c>
       <c r="D6">
-        <v>31.75194243081729</v>
+        <v>31.85100056535162</v>
       </c>
       <c r="E6">
-        <v>-24.4816</v>
+        <v>-24.127</v>
       </c>
       <c r="F6">
-        <v>1.4184</v>
+        <v>1.773</v>
       </c>
       <c r="G6">
         <v>4.13</v>
@@ -2410,28 +2410,28 @@
         <v>1.288</v>
       </c>
       <c r="M6">
-        <v>0.07134552</v>
+        <v>0.08918190000000001</v>
       </c>
       <c r="N6">
-        <v>1.21665448</v>
+        <v>1.1988181</v>
       </c>
       <c r="O6">
-        <v>0.2676639856</v>
+        <v>0.2637399819999999</v>
       </c>
       <c r="P6">
-        <v>0.9489904943999998</v>
+        <v>0.9350781179999998</v>
       </c>
       <c r="Q6">
-        <v>1.2969904944</v>
+        <v>1.283078118</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1235601930961174</v>
+        <v>0.1242043134671187</v>
       </c>
       <c r="T6">
-        <v>1.01347599165141</v>
+        <v>1.021871039371219</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.05299057319927</v>
+        <v>14.44239245855941</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2456,22 +2456,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1199557977937628</v>
+        <v>0.1197946502152529</v>
       </c>
       <c r="C7">
-        <v>34.20800056535162</v>
+        <v>33.92276654788269</v>
       </c>
       <c r="D7">
-        <v>31.85100056535162</v>
+        <v>31.9203665478827</v>
       </c>
       <c r="E7">
-        <v>-24.127</v>
+        <v>-23.7724</v>
       </c>
       <c r="F7">
-        <v>1.773</v>
+        <v>2.1276</v>
       </c>
       <c r="G7">
         <v>4.13</v>
@@ -2492,45 +2492,45 @@
         <v>1.288</v>
       </c>
       <c r="M7">
-        <v>0.08918190000000001</v>
+        <v>0.11020968</v>
       </c>
       <c r="N7">
-        <v>1.1988181</v>
+        <v>1.17779032</v>
       </c>
       <c r="O7">
-        <v>0.2637399819999999</v>
+        <v>0.2591138703999999</v>
       </c>
       <c r="P7">
-        <v>0.9350781179999998</v>
+        <v>0.9186764495999997</v>
       </c>
       <c r="Q7">
-        <v>1.283078118</v>
+        <v>1.2666764496</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1242043134671187</v>
+        <v>0.1248621385268648</v>
       </c>
       <c r="T7">
-        <v>1.021871039371219</v>
+        <v>1.03044470512762</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.44239245855941</v>
+        <v>11.68681371727057</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2538,22 +2538,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1197946502152529</v>
+        <v>0.119575002636743</v>
       </c>
       <c r="C8">
-        <v>33.92276654788269</v>
+        <v>33.66320187105188</v>
       </c>
       <c r="D8">
-        <v>31.9203665478827</v>
+        <v>32.01540187105188</v>
       </c>
       <c r="E8">
-        <v>-23.7724</v>
+        <v>-23.4178</v>
       </c>
       <c r="F8">
-        <v>2.1276</v>
+        <v>2.4822</v>
       </c>
       <c r="G8">
         <v>4.13</v>
@@ -2574,28 +2574,28 @@
         <v>1.288</v>
       </c>
       <c r="M8">
-        <v>0.11020968</v>
+        <v>0.12857796</v>
       </c>
       <c r="N8">
-        <v>1.17779032</v>
+        <v>1.15942204</v>
       </c>
       <c r="O8">
-        <v>0.2591138703999999</v>
+        <v>0.2550728488</v>
       </c>
       <c r="P8">
-        <v>0.9186764495999997</v>
+        <v>0.9043491911999999</v>
       </c>
       <c r="Q8">
-        <v>1.2666764496</v>
+        <v>1.2523491912</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1248621385268648</v>
+        <v>0.1255341103620893</v>
       </c>
       <c r="T8">
-        <v>1.03044470512762</v>
+        <v>1.03920275079276</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.68681371727057</v>
+        <v>10.01726890051763</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2620,22 +2620,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.119575002636743</v>
+        <v>0.1194614350582331</v>
       </c>
       <c r="C9">
-        <v>33.66320187105188</v>
+        <v>33.35796164340279</v>
       </c>
       <c r="D9">
-        <v>32.01540187105188</v>
+        <v>32.06476164340279</v>
       </c>
       <c r="E9">
-        <v>-23.4178</v>
+        <v>-23.0632</v>
       </c>
       <c r="F9">
-        <v>2.4822</v>
+        <v>2.8368</v>
       </c>
       <c r="G9">
         <v>4.13</v>
@@ -2656,45 +2656,45 @@
         <v>1.288</v>
       </c>
       <c r="M9">
-        <v>0.12857796</v>
+        <v>0.1517688</v>
       </c>
       <c r="N9">
-        <v>1.15942204</v>
+        <v>1.1362312</v>
       </c>
       <c r="O9">
-        <v>0.2550728487999999</v>
+        <v>0.249970864</v>
       </c>
       <c r="P9">
-        <v>0.9043491911999998</v>
+        <v>0.8862603359999999</v>
       </c>
       <c r="Q9">
-        <v>1.2523491912</v>
+        <v>1.234260336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1255341103620893</v>
+        <v>0.1262206902806882</v>
       </c>
       <c r="T9">
-        <v>1.039202750792761</v>
+        <v>1.048151188754969</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.01726890051763</v>
+        <v>8.486592764784328</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2702,22 +2702,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1194614350582331</v>
+        <v>0.1193112074797233</v>
       </c>
       <c r="C10">
-        <v>33.35796164340279</v>
+        <v>33.06888922296966</v>
       </c>
       <c r="D10">
-        <v>32.06476164340279</v>
+        <v>32.13028922296966</v>
       </c>
       <c r="E10">
-        <v>-23.0632</v>
+        <v>-22.7086</v>
       </c>
       <c r="F10">
-        <v>2.8368</v>
+        <v>3.1914</v>
       </c>
       <c r="G10">
         <v>4.13</v>
@@ -2738,45 +2738,45 @@
         <v>1.288</v>
       </c>
       <c r="M10">
-        <v>0.1517688</v>
+        <v>0.17329302</v>
       </c>
       <c r="N10">
-        <v>1.1362312</v>
+        <v>1.11470698</v>
       </c>
       <c r="O10">
-        <v>0.249970864</v>
+        <v>0.2452355355999999</v>
       </c>
       <c r="P10">
-        <v>0.8862603359999999</v>
+        <v>0.8694714443999998</v>
       </c>
       <c r="Q10">
-        <v>1.234260336</v>
+        <v>1.2174714444</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1262206902806882</v>
+        <v>0.1269223598678278</v>
       </c>
       <c r="T10">
-        <v>1.048151188754969</v>
+        <v>1.057296295683381</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.486592764784328</v>
+        <v>7.432497858251878</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2784,22 +2784,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1193112074797233</v>
+        <v>0.1191110599012133</v>
       </c>
       <c r="C11">
-        <v>33.06888922296966</v>
+        <v>32.80200858746209</v>
       </c>
       <c r="D11">
-        <v>32.13028922296966</v>
+        <v>32.21800858746209</v>
       </c>
       <c r="E11">
-        <v>-22.7086</v>
+        <v>-22.354</v>
       </c>
       <c r="F11">
-        <v>3.1914</v>
+        <v>3.546</v>
       </c>
       <c r="G11">
         <v>4.13</v>
@@ -2820,28 +2820,28 @@
         <v>1.288</v>
       </c>
       <c r="M11">
-        <v>0.17329302</v>
+        <v>0.1925478</v>
       </c>
       <c r="N11">
-        <v>1.11470698</v>
+        <v>1.0954522</v>
       </c>
       <c r="O11">
-        <v>0.2452355355999999</v>
+        <v>0.240999484</v>
       </c>
       <c r="P11">
-        <v>0.8694714443999998</v>
+        <v>0.8544527159999998</v>
       </c>
       <c r="Q11">
-        <v>1.2174714444</v>
+        <v>1.202452716</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1269223598678278</v>
+        <v>0.1276396221124593</v>
       </c>
       <c r="T11">
-        <v>1.057296295683381</v>
+        <v>1.066644627210201</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.432497858251878</v>
+        <v>6.68924807242669</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2866,22 +2866,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1191110599012133</v>
+        <v>0.1189967123227035</v>
       </c>
       <c r="C12">
-        <v>32.80200858746209</v>
+        <v>32.49773941721501</v>
       </c>
       <c r="D12">
-        <v>32.21800858746209</v>
+        <v>32.268339417215</v>
       </c>
       <c r="E12">
-        <v>-22.354</v>
+        <v>-21.9994</v>
       </c>
       <c r="F12">
-        <v>3.546</v>
+        <v>3.9006</v>
       </c>
       <c r="G12">
         <v>4.13</v>
@@ -2902,45 +2902,45 @@
         <v>1.288</v>
       </c>
       <c r="M12">
-        <v>0.1925478</v>
+        <v>0.21570318</v>
       </c>
       <c r="N12">
-        <v>1.0954522</v>
+        <v>1.07229682</v>
       </c>
       <c r="O12">
-        <v>0.240999484</v>
+        <v>0.2359053004</v>
       </c>
       <c r="P12">
-        <v>0.8544527159999998</v>
+        <v>0.8363915195999998</v>
       </c>
       <c r="Q12">
-        <v>1.202452716</v>
+        <v>1.1843915196</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1276396221124593</v>
+        <v>0.1283730026097792</v>
       </c>
       <c r="T12">
-        <v>1.066644627210201</v>
+        <v>1.076203033602793</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.689248072426689</v>
+        <v>5.971168343461602</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2948,22 +2948,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1189967123227035</v>
+        <v>0.1188043647441936</v>
       </c>
       <c r="C13">
-        <v>32.49773941721501</v>
+        <v>32.22815812768778</v>
       </c>
       <c r="D13">
-        <v>32.268339417215</v>
+        <v>32.35335812768778</v>
       </c>
       <c r="E13">
-        <v>-21.9994</v>
+        <v>-21.6448</v>
       </c>
       <c r="F13">
-        <v>3.9006</v>
+        <v>4.2552</v>
       </c>
       <c r="G13">
         <v>4.13</v>
@@ -2984,28 +2984,28 @@
         <v>1.288</v>
       </c>
       <c r="M13">
-        <v>0.21570318</v>
+        <v>0.23531256</v>
       </c>
       <c r="N13">
-        <v>1.07229682</v>
+        <v>1.05268744</v>
       </c>
       <c r="O13">
-        <v>0.2359053004</v>
+        <v>0.2315912367999999</v>
       </c>
       <c r="P13">
-        <v>0.8363915195999998</v>
+        <v>0.8210962031999998</v>
       </c>
       <c r="Q13">
-        <v>1.1843915196</v>
+        <v>1.1690962032</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1283730026097792</v>
+        <v>0.1291230508456745</v>
       </c>
       <c r="T13">
-        <v>1.076203033602793</v>
+        <v>1.085978676504307</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.971168343461602</v>
+        <v>5.473570981506468</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3030,22 +3030,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1188043647441936</v>
+        <v>0.1186120171656837</v>
       </c>
       <c r="C14">
-        <v>32.22815812768778</v>
+        <v>31.95902602618541</v>
       </c>
       <c r="D14">
-        <v>32.35335812768778</v>
+        <v>32.43882602618541</v>
       </c>
       <c r="E14">
-        <v>-21.6448</v>
+        <v>-21.2902</v>
       </c>
       <c r="F14">
-        <v>4.2552</v>
+        <v>4.6098</v>
       </c>
       <c r="G14">
         <v>4.13</v>
@@ -3066,28 +3066,28 @@
         <v>1.288</v>
       </c>
       <c r="M14">
-        <v>0.23531256</v>
+        <v>0.25492194</v>
       </c>
       <c r="N14">
-        <v>1.05268744</v>
+        <v>1.03307806</v>
       </c>
       <c r="O14">
-        <v>0.2315912367999999</v>
+        <v>0.2272771732</v>
       </c>
       <c r="P14">
-        <v>0.8210962031999998</v>
+        <v>0.8058008867999998</v>
       </c>
       <c r="Q14">
-        <v>1.1690962032</v>
+        <v>1.1538008868</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1291230508456745</v>
+        <v>0.1298903415697514</v>
       </c>
       <c r="T14">
-        <v>1.085978676504307</v>
+        <v>1.095979046828844</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.473570981506468</v>
+        <v>5.052527059852125</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3112,22 +3112,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1186120171656837</v>
+        <v>0.1184196695871738</v>
       </c>
       <c r="C15">
-        <v>31.95902602618541</v>
+        <v>31.69034668199823</v>
       </c>
       <c r="D15">
-        <v>32.43882602618541</v>
+        <v>32.52474668199823</v>
       </c>
       <c r="E15">
-        <v>-21.2902</v>
+        <v>-20.9356</v>
       </c>
       <c r="F15">
-        <v>4.6098</v>
+        <v>4.9644</v>
       </c>
       <c r="G15">
         <v>4.13</v>
@@ -3148,28 +3148,28 @@
         <v>1.288</v>
       </c>
       <c r="M15">
-        <v>0.25492194</v>
+        <v>0.27453132</v>
       </c>
       <c r="N15">
-        <v>1.03307806</v>
+        <v>1.01346868</v>
       </c>
       <c r="O15">
-        <v>0.2272771732</v>
+        <v>0.2229631096</v>
       </c>
       <c r="P15">
-        <v>0.8058008867999998</v>
+        <v>0.7905055703999999</v>
       </c>
       <c r="Q15">
-        <v>1.1538008868</v>
+        <v>1.1385055704</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1298903415697514</v>
+        <v>0.1306754762641556</v>
       </c>
       <c r="T15">
-        <v>1.095979046828844</v>
+        <v>1.106211983905115</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.052527059852125</v>
+        <v>4.691632269862687</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3194,22 +3194,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1184196695871738</v>
+        <v>0.1185198220086639</v>
       </c>
       <c r="C16">
-        <v>31.69034668199823</v>
+        <v>31.29095240103634</v>
       </c>
       <c r="D16">
-        <v>32.52474668199823</v>
+        <v>32.47995240103634</v>
       </c>
       <c r="E16">
-        <v>-20.9356</v>
+        <v>-20.581</v>
       </c>
       <c r="F16">
-        <v>4.9644</v>
+        <v>5.319000000000001</v>
       </c>
       <c r="G16">
         <v>4.13</v>
@@ -3230,45 +3230,45 @@
         <v>1.288</v>
       </c>
       <c r="M16">
-        <v>0.27453132</v>
+        <v>0.3074382000000001</v>
       </c>
       <c r="N16">
-        <v>1.01346868</v>
+        <v>0.9805617999999998</v>
       </c>
       <c r="O16">
-        <v>0.2229631096</v>
+        <v>0.215723596</v>
       </c>
       <c r="P16">
-        <v>0.7905055703999999</v>
+        <v>0.7648382039999999</v>
       </c>
       <c r="Q16">
-        <v>1.1385055704</v>
+        <v>1.112838204</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1306754762641556</v>
+        <v>0.1314790847160752</v>
       </c>
       <c r="T16">
-        <v>1.106211983905115</v>
+        <v>1.116685695971416</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.691632269862687</v>
+        <v>4.189459865429864</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3276,22 +3276,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1185198220086639</v>
+        <v>0.118783774430154</v>
       </c>
       <c r="C17">
-        <v>31.29095240103635</v>
+        <v>30.81888571541923</v>
       </c>
       <c r="D17">
-        <v>32.47995240103635</v>
+        <v>32.36248571541923</v>
       </c>
       <c r="E17">
-        <v>-20.581</v>
+        <v>-20.2264</v>
       </c>
       <c r="F17">
-        <v>5.319</v>
+        <v>5.6736</v>
       </c>
       <c r="G17">
         <v>4.13</v>
@@ -3312,45 +3312,45 @@
         <v>1.288</v>
       </c>
       <c r="M17">
-        <v>0.3074382</v>
+        <v>0.34779168</v>
       </c>
       <c r="N17">
-        <v>0.9805617999999998</v>
+        <v>0.9402083199999998</v>
       </c>
       <c r="O17">
-        <v>0.215723596</v>
+        <v>0.2068458304</v>
       </c>
       <c r="P17">
-        <v>0.7648382039999999</v>
+        <v>0.7333624895999998</v>
       </c>
       <c r="Q17">
-        <v>1.112838204</v>
+        <v>1.0813624896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1314790847160752</v>
+        <v>0.1323018267025643</v>
       </c>
       <c r="T17">
-        <v>1.116685695971416</v>
+        <v>1.127408782134533</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.189459865429865</v>
+        <v>3.703366336998055</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3358,22 +3358,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.118783774430154</v>
+        <v>0.1190095068516442</v>
       </c>
       <c r="C18">
-        <v>30.81888571541923</v>
+        <v>30.36450001025412</v>
       </c>
       <c r="D18">
-        <v>32.36248571541923</v>
+        <v>32.26270001025412</v>
       </c>
       <c r="E18">
-        <v>-20.2264</v>
+        <v>-19.8718</v>
       </c>
       <c r="F18">
-        <v>5.6736</v>
+        <v>6.028200000000001</v>
       </c>
       <c r="G18">
         <v>4.13</v>
@@ -3394,45 +3394,45 @@
         <v>1.288</v>
       </c>
       <c r="M18">
-        <v>0.34779168</v>
+        <v>0.3864076200000001</v>
       </c>
       <c r="N18">
-        <v>0.9402083199999998</v>
+        <v>0.9015923799999997</v>
       </c>
       <c r="O18">
-        <v>0.2068458304</v>
+        <v>0.1983503235999999</v>
       </c>
       <c r="P18">
-        <v>0.7333624895999998</v>
+        <v>0.7032420563999998</v>
       </c>
       <c r="Q18">
-        <v>1.0813624896</v>
+        <v>1.0512420564</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1323018267025643</v>
+        <v>0.1331443937971616</v>
       </c>
       <c r="T18">
-        <v>1.127408782134533</v>
+        <v>1.138390255916039</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.703366336998055</v>
+        <v>3.333267599639985</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3440,22 +3440,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1190095068516442</v>
+        <v>0.1188857992731343</v>
       </c>
       <c r="C19">
-        <v>30.36450001025412</v>
+        <v>30.06450898401036</v>
       </c>
       <c r="D19">
-        <v>32.26270001025412</v>
+        <v>32.31730898401035</v>
       </c>
       <c r="E19">
-        <v>-19.8718</v>
+        <v>-19.5172</v>
       </c>
       <c r="F19">
-        <v>6.028200000000001</v>
+        <v>6.3828</v>
       </c>
       <c r="G19">
         <v>4.13</v>
@@ -3476,28 +3476,28 @@
         <v>1.288</v>
       </c>
       <c r="M19">
-        <v>0.3864076200000001</v>
+        <v>0.4091374800000001</v>
       </c>
       <c r="N19">
-        <v>0.9015923799999997</v>
+        <v>0.8788625199999998</v>
       </c>
       <c r="O19">
-        <v>0.1983503235999999</v>
+        <v>0.1933497543999999</v>
       </c>
       <c r="P19">
-        <v>0.7032420563999998</v>
+        <v>0.6855127655999999</v>
       </c>
       <c r="Q19">
-        <v>1.0512420564</v>
+        <v>1.0335127656</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1331443937971616</v>
+        <v>0.1340075113087003</v>
       </c>
       <c r="T19">
-        <v>1.138390255916039</v>
+        <v>1.149639570521484</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.333267599639985</v>
+        <v>3.148086066326653</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3522,22 +3522,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1188857992731343</v>
+        <v>0.1199180516946244</v>
       </c>
       <c r="C20">
-        <v>30.06450898401036</v>
+        <v>29.25982132395913</v>
       </c>
       <c r="D20">
-        <v>32.31730898401036</v>
+        <v>31.86722132395913</v>
       </c>
       <c r="E20">
-        <v>-19.5172</v>
+        <v>-19.1626</v>
       </c>
       <c r="F20">
-        <v>6.3828</v>
+        <v>6.7374</v>
       </c>
       <c r="G20">
         <v>4.13</v>
@@ -3558,45 +3558,45 @@
         <v>1.288</v>
       </c>
       <c r="M20">
-        <v>0.40913748</v>
+        <v>0.4844190600000001</v>
       </c>
       <c r="N20">
-        <v>0.8788625199999998</v>
+        <v>0.8035809399999998</v>
       </c>
       <c r="O20">
-        <v>0.1933497543999999</v>
+        <v>0.1767878067999999</v>
       </c>
       <c r="P20">
-        <v>0.6855127655999999</v>
+        <v>0.6267931331999999</v>
       </c>
       <c r="Q20">
-        <v>1.0335127656</v>
+        <v>0.9747931331999998</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1340075113087003</v>
+        <v>0.1348919403637338</v>
       </c>
       <c r="T20">
-        <v>1.149639570521484</v>
+        <v>1.161166645981384</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.148086066326653</v>
+        <v>2.658854917888656</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3604,22 +3604,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1199180516946244</v>
+        <v>0.1198551841161145</v>
       </c>
       <c r="C21">
-        <v>29.25982132395913</v>
+        <v>28.93227432588449</v>
       </c>
       <c r="D21">
-        <v>31.86722132395913</v>
+        <v>31.89427432588449</v>
       </c>
       <c r="E21">
-        <v>-19.1626</v>
+        <v>-18.808</v>
       </c>
       <c r="F21">
-        <v>6.7374</v>
+        <v>7.092000000000001</v>
       </c>
       <c r="G21">
         <v>4.13</v>
@@ -3640,28 +3640,28 @@
         <v>1.288</v>
       </c>
       <c r="M21">
-        <v>0.4844190600000001</v>
+        <v>0.5099148000000001</v>
       </c>
       <c r="N21">
-        <v>0.8035809399999998</v>
+        <v>0.7780851999999997</v>
       </c>
       <c r="O21">
-        <v>0.1767878067999999</v>
+        <v>0.1711787439999999</v>
       </c>
       <c r="P21">
-        <v>0.6267931331999999</v>
+        <v>0.6069064559999997</v>
       </c>
       <c r="Q21">
-        <v>0.9747931331999998</v>
+        <v>0.9549064559999997</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1348919403637338</v>
+        <v>0.1357984801451431</v>
       </c>
       <c r="T21">
-        <v>1.161166645981384</v>
+        <v>1.172981898327782</v>
       </c>
       <c r="U21">
         <v>0.07190000000000001</v>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.658854917888656</v>
+        <v>2.525912171994222</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3686,22 +3686,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1198551841161145</v>
+        <v>0.1204311365376046</v>
       </c>
       <c r="C22">
-        <v>28.93227432588449</v>
+        <v>28.33153597958706</v>
       </c>
       <c r="D22">
-        <v>31.89427432588449</v>
+        <v>31.64813597958706</v>
       </c>
       <c r="E22">
-        <v>-18.808</v>
+        <v>-18.4534</v>
       </c>
       <c r="F22">
-        <v>7.092000000000001</v>
+        <v>7.446600000000001</v>
       </c>
       <c r="G22">
         <v>4.13</v>
@@ -3722,45 +3722,45 @@
         <v>1.288</v>
       </c>
       <c r="M22">
-        <v>0.5099148000000001</v>
+        <v>0.5644522800000001</v>
       </c>
       <c r="N22">
-        <v>0.7780851999999997</v>
+        <v>0.7235477199999997</v>
       </c>
       <c r="O22">
-        <v>0.1711787439999999</v>
+        <v>0.1591804983999999</v>
       </c>
       <c r="P22">
-        <v>0.6069064559999997</v>
+        <v>0.5643672215999997</v>
       </c>
       <c r="Q22">
-        <v>0.9549064559999997</v>
+        <v>0.9123672215999997</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1357984801451431</v>
+        <v>0.1367279703007653</v>
       </c>
       <c r="T22">
-        <v>1.172981898327782</v>
+        <v>1.185096270986747</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.525912171994222</v>
+        <v>2.281858087277103</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3768,22 +3768,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1204311365376046</v>
+        <v>0.1203986889590947</v>
       </c>
       <c r="C23">
-        <v>28.33153597958708</v>
+        <v>27.99070170913564</v>
       </c>
       <c r="D23">
-        <v>31.64813597958707</v>
+        <v>31.66190170913564</v>
       </c>
       <c r="E23">
-        <v>-18.4534</v>
+        <v>-18.0988</v>
       </c>
       <c r="F23">
-        <v>7.4466</v>
+        <v>7.801200000000001</v>
       </c>
       <c r="G23">
         <v>4.13</v>
@@ -3804,28 +3804,28 @@
         <v>1.288</v>
       </c>
       <c r="M23">
-        <v>0.56445228</v>
+        <v>0.5913309600000001</v>
       </c>
       <c r="N23">
-        <v>0.7235477199999998</v>
+        <v>0.6966690399999997</v>
       </c>
       <c r="O23">
-        <v>0.1591804984</v>
+        <v>0.1532671888</v>
       </c>
       <c r="P23">
-        <v>0.5643672215999999</v>
+        <v>0.5434018511999998</v>
       </c>
       <c r="Q23">
-        <v>0.9123672215999998</v>
+        <v>0.8914018511999998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1367279703007653</v>
+        <v>0.1376812935373009</v>
       </c>
       <c r="T23">
-        <v>1.185096270986747</v>
+        <v>1.197521268585686</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.281858087277103</v>
+        <v>2.178137265128144</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3850,22 +3850,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1203986889590947</v>
+        <v>0.1203662413805848</v>
       </c>
       <c r="C24">
-        <v>27.99070170913564</v>
+        <v>27.64987941902766</v>
       </c>
       <c r="D24">
-        <v>31.66190170913564</v>
+        <v>31.67567941902766</v>
       </c>
       <c r="E24">
-        <v>-18.0988</v>
+        <v>-17.7442</v>
       </c>
       <c r="F24">
-        <v>7.801200000000001</v>
+        <v>8.155800000000001</v>
       </c>
       <c r="G24">
         <v>4.13</v>
@@ -3886,28 +3886,28 @@
         <v>1.288</v>
       </c>
       <c r="M24">
-        <v>0.5913309600000001</v>
+        <v>0.6182096400000001</v>
       </c>
       <c r="N24">
-        <v>0.6966690399999997</v>
+        <v>0.6697903599999997</v>
       </c>
       <c r="O24">
-        <v>0.1532671888</v>
+        <v>0.1473538791999999</v>
       </c>
       <c r="P24">
-        <v>0.5434018511999998</v>
+        <v>0.5224364807999997</v>
       </c>
       <c r="Q24">
-        <v>0.8914018511999998</v>
+        <v>0.8704364807999997</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1376812935373009</v>
+        <v>0.1386593784163439</v>
       </c>
       <c r="T24">
-        <v>1.197521268585686</v>
+        <v>1.210268993394986</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.178137265128144</v>
+        <v>2.083435644905181</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3932,22 +3932,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1203662413805848</v>
+        <v>0.1229920338020749</v>
       </c>
       <c r="C25">
-        <v>27.64987941902766</v>
+        <v>26.21778793619803</v>
       </c>
       <c r="D25">
-        <v>31.67567941902766</v>
+        <v>30.59818793619802</v>
       </c>
       <c r="E25">
-        <v>-17.7442</v>
+        <v>-17.3896</v>
       </c>
       <c r="F25">
-        <v>8.155800000000001</v>
+        <v>8.510400000000001</v>
       </c>
       <c r="G25">
         <v>4.13</v>
@@ -3968,45 +3968,45 @@
         <v>1.288</v>
       </c>
       <c r="M25">
-        <v>0.6182096400000001</v>
+        <v>0.7659360000000001</v>
       </c>
       <c r="N25">
-        <v>0.6697903599999997</v>
+        <v>0.5220639999999998</v>
       </c>
       <c r="O25">
-        <v>0.1473538791999999</v>
+        <v>0.1148540799999999</v>
       </c>
       <c r="P25">
-        <v>0.5224364807999997</v>
+        <v>0.4072099199999998</v>
       </c>
       <c r="Q25">
-        <v>0.8704364807999997</v>
+        <v>0.7552099199999998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1386593784163439</v>
+        <v>0.1396632023711512</v>
       </c>
       <c r="T25">
-        <v>1.210268993394986</v>
+        <v>1.223352184646637</v>
       </c>
       <c r="U25">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.083435644905181</v>
+        <v>1.681602640429487</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -4014,22 +4014,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1229920338020749</v>
+        <v>0.123070346223565</v>
       </c>
       <c r="C26">
-        <v>26.21778793619803</v>
+        <v>25.83217709817797</v>
       </c>
       <c r="D26">
-        <v>30.59818793619802</v>
+        <v>30.56717709817797</v>
       </c>
       <c r="E26">
-        <v>-17.3896</v>
+        <v>-17.035</v>
       </c>
       <c r="F26">
-        <v>8.510400000000001</v>
+        <v>8.865</v>
       </c>
       <c r="G26">
         <v>4.13</v>
@@ -4050,28 +4050,28 @@
         <v>1.288</v>
       </c>
       <c r="M26">
-        <v>0.7659360000000001</v>
+        <v>0.7978499999999999</v>
       </c>
       <c r="N26">
-        <v>0.5220639999999998</v>
+        <v>0.4901499999999999</v>
       </c>
       <c r="O26">
-        <v>0.1148540799999999</v>
+        <v>0.107833</v>
       </c>
       <c r="P26">
-        <v>0.4072099199999998</v>
+        <v>0.3823169999999999</v>
       </c>
       <c r="Q26">
-        <v>0.7552099199999998</v>
+        <v>0.7303169999999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1396632023711512</v>
+        <v>0.1406937949647534</v>
       </c>
       <c r="T26">
-        <v>1.223352184646637</v>
+        <v>1.236784260998331</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.681602640429487</v>
+        <v>1.614338534812308</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -4096,22 +4096,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.123070346223565</v>
+        <v>0.1231486586450552</v>
       </c>
       <c r="C27">
-        <v>25.83217709817797</v>
+        <v>25.44662905462286</v>
       </c>
       <c r="D27">
-        <v>30.56717709817797</v>
+        <v>30.53622905462286</v>
       </c>
       <c r="E27">
-        <v>-17.035</v>
+        <v>-16.6804</v>
       </c>
       <c r="F27">
-        <v>8.865</v>
+        <v>9.2196</v>
       </c>
       <c r="G27">
         <v>4.13</v>
@@ -4132,28 +4132,28 @@
         <v>1.288</v>
       </c>
       <c r="M27">
-        <v>0.7978499999999999</v>
+        <v>0.8297639999999999</v>
       </c>
       <c r="N27">
-        <v>0.4901499999999999</v>
+        <v>0.4582359999999999</v>
       </c>
       <c r="O27">
-        <v>0.107833</v>
+        <v>0.10081192</v>
       </c>
       <c r="P27">
-        <v>0.3823169999999999</v>
+        <v>0.3574240799999999</v>
       </c>
       <c r="Q27">
-        <v>0.7303169999999999</v>
+        <v>0.7054240799999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1406937949647534</v>
+        <v>0.1417522414122367</v>
       </c>
       <c r="T27">
-        <v>1.236784260998331</v>
+        <v>1.250579366440612</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.614338534812308</v>
+        <v>1.552248591165681</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4178,22 +4178,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1231486586450552</v>
+        <v>0.1362919642568485</v>
       </c>
       <c r="C28">
-        <v>25.44662905462286</v>
+        <v>20.6568618661036</v>
       </c>
       <c r="D28">
-        <v>30.53622905462286</v>
+        <v>26.1010618661036</v>
       </c>
       <c r="E28">
-        <v>-16.6804</v>
+        <v>-16.3258</v>
       </c>
       <c r="F28">
-        <v>9.2196</v>
+        <v>9.574200000000001</v>
       </c>
       <c r="G28">
         <v>4.13</v>
@@ -4214,45 +4214,45 @@
         <v>1.288</v>
       </c>
       <c r="M28">
-        <v>0.8297639999999999</v>
+        <v>1.40549256</v>
       </c>
       <c r="N28">
-        <v>0.4582359999999999</v>
+        <v>-0.1174925600000005</v>
       </c>
       <c r="O28">
-        <v>0.10081192</v>
+        <v>-0.02584836320000012</v>
       </c>
       <c r="P28">
-        <v>0.3574240799999999</v>
+        <v>-0.09164419680000041</v>
       </c>
       <c r="Q28">
-        <v>0.7054240799999999</v>
+        <v>0.2563558031999996</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1417522414122367</v>
+        <v>0.1433519726084513</v>
       </c>
       <c r="T28">
-        <v>1.250579366440612</v>
+        <v>1.271429226708516</v>
       </c>
       <c r="U28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.22</v>
+        <v>0.2016090359098023</v>
       </c>
       <c r="W28">
-        <v>0.0702</v>
+        <v>0.117203793528441</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.552248591165681</v>
+        <v>0.9164047086809193</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4260,22 +4260,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1362919642568485</v>
+        <v>0.1373019642568485</v>
       </c>
       <c r="C29">
-        <v>20.6568618661036</v>
+        <v>20.01415796911222</v>
       </c>
       <c r="D29">
-        <v>26.1010618661036</v>
+        <v>25.81295796911222</v>
       </c>
       <c r="E29">
-        <v>-16.3258</v>
+        <v>-15.9712</v>
       </c>
       <c r="F29">
-        <v>9.574200000000001</v>
+        <v>9.928800000000001</v>
       </c>
       <c r="G29">
         <v>4.13</v>
@@ -4296,37 +4296,37 @@
         <v>1.288</v>
       </c>
       <c r="M29">
-        <v>1.40549256</v>
+        <v>1.45754784</v>
       </c>
       <c r="N29">
-        <v>-0.1174925600000005</v>
+        <v>-0.1695478400000003</v>
       </c>
       <c r="O29">
-        <v>-0.02584836320000012</v>
+        <v>-0.03730052480000007</v>
       </c>
       <c r="P29">
-        <v>-0.09164419680000041</v>
+        <v>-0.1322473152000003</v>
       </c>
       <c r="Q29">
-        <v>0.2563558031999996</v>
+        <v>0.2157526847999997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1433519726084513</v>
+        <v>0.144706861116902</v>
       </c>
       <c r="T29">
-        <v>1.271429226708516</v>
+        <v>1.289087965968356</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.2016090359098023</v>
+        <v>0.1944087131987379</v>
       </c>
       <c r="W29">
-        <v>0.117203793528441</v>
+        <v>0.1182608009024253</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.9164047086809193</v>
+        <v>0.8836759690851723</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4342,22 +4342,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1373019642568485</v>
+        <v>0.1383119642568485</v>
       </c>
       <c r="C30">
-        <v>20.01415796911222</v>
+        <v>19.37774482463698</v>
       </c>
       <c r="D30">
-        <v>25.81295796911222</v>
+        <v>25.53114482463698</v>
       </c>
       <c r="E30">
-        <v>-15.9712</v>
+        <v>-15.6166</v>
       </c>
       <c r="F30">
-        <v>9.928800000000001</v>
+        <v>10.2834</v>
       </c>
       <c r="G30">
         <v>4.13</v>
@@ -4378,37 +4378,37 @@
         <v>1.288</v>
       </c>
       <c r="M30">
-        <v>1.45754784</v>
+        <v>1.50960312</v>
       </c>
       <c r="N30">
-        <v>-0.1695478400000003</v>
+        <v>-0.2216031200000006</v>
       </c>
       <c r="O30">
-        <v>-0.03730052480000007</v>
+        <v>-0.04875268640000013</v>
       </c>
       <c r="P30">
-        <v>-0.1322473152000003</v>
+        <v>-0.1728504336000005</v>
       </c>
       <c r="Q30">
-        <v>0.2157526847999997</v>
+        <v>0.1751495663999995</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.144706861116902</v>
+        <v>0.1460999154988302</v>
       </c>
       <c r="T30">
-        <v>1.289087965968356</v>
+        <v>1.307244134503122</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.1944087131987379</v>
+        <v>0.1877049644677469</v>
       </c>
       <c r="W30">
-        <v>0.1182608009024253</v>
+        <v>0.1192449112161348</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8836759690851723</v>
+        <v>0.8532043839443042</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4424,22 +4424,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1383119642568485</v>
+        <v>0.1393219642568485</v>
       </c>
       <c r="C31">
-        <v>19.37774482463698</v>
+        <v>18.74741861980596</v>
       </c>
       <c r="D31">
-        <v>25.53114482463699</v>
+        <v>25.25541861980596</v>
       </c>
       <c r="E31">
-        <v>-15.6166</v>
+        <v>-15.262</v>
       </c>
       <c r="F31">
-        <v>10.2834</v>
+        <v>10.638</v>
       </c>
       <c r="G31">
         <v>4.13</v>
@@ -4460,37 +4460,37 @@
         <v>1.288</v>
       </c>
       <c r="M31">
-        <v>1.50960312</v>
+        <v>1.5616584</v>
       </c>
       <c r="N31">
-        <v>-0.2216031200000004</v>
+        <v>-0.2736584000000004</v>
       </c>
       <c r="O31">
-        <v>-0.04875268640000009</v>
+        <v>-0.06020484800000009</v>
       </c>
       <c r="P31">
-        <v>-0.1728504336000003</v>
+        <v>-0.2134535520000003</v>
       </c>
       <c r="Q31">
-        <v>0.1751495663999997</v>
+        <v>0.1345464479999997</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1460999154988302</v>
+        <v>0.1475327714345278</v>
       </c>
       <c r="T31">
-        <v>1.307244134503122</v>
+        <v>1.325919050710309</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.187704964467747</v>
+        <v>0.181448132318822</v>
       </c>
       <c r="W31">
-        <v>0.1192449112161348</v>
+        <v>0.1201634141755969</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8532043839443043</v>
+        <v>0.8247642378128275</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4506,22 +4506,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1393219642568485</v>
+        <v>0.1581744451673849</v>
       </c>
       <c r="C32">
-        <v>18.74741861980596</v>
+        <v>14.15584733413427</v>
       </c>
       <c r="D32">
-        <v>25.25541861980596</v>
+        <v>21.01844733413427</v>
       </c>
       <c r="E32">
-        <v>-15.262</v>
+        <v>-14.9074</v>
       </c>
       <c r="F32">
-        <v>10.638</v>
+        <v>10.9926</v>
       </c>
       <c r="G32">
         <v>4.13</v>
@@ -4542,45 +4542,45 @@
         <v>1.288</v>
       </c>
       <c r="M32">
-        <v>1.5616584</v>
+        <v>2.20731408</v>
       </c>
       <c r="N32">
-        <v>-0.2736584000000004</v>
+        <v>-0.9193140800000004</v>
       </c>
       <c r="O32">
-        <v>-0.06020484800000009</v>
+        <v>-0.2022490976000001</v>
       </c>
       <c r="P32">
-        <v>-0.2134535520000003</v>
+        <v>-0.7170649824000003</v>
       </c>
       <c r="Q32">
-        <v>0.1345464479999997</v>
+        <v>-0.3690649824000003</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1475327714345278</v>
+        <v>0.1506049578473998</v>
       </c>
       <c r="T32">
-        <v>1.325919050710309</v>
+        <v>1.365959938565035</v>
       </c>
       <c r="U32">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.181448132318822</v>
+        <v>0.1283732127509466</v>
       </c>
       <c r="W32">
-        <v>0.1201634141755969</v>
+        <v>0.1750226588796099</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.8247642378128275</v>
+        <v>0.5835146034133936</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4588,22 +4588,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1581744451673849</v>
+        <v>0.1597244451673849</v>
       </c>
       <c r="C33">
-        <v>14.15584733413427</v>
+        <v>13.51528067157961</v>
       </c>
       <c r="D33">
-        <v>21.01844733413427</v>
+        <v>20.73248067157962</v>
       </c>
       <c r="E33">
-        <v>-14.9074</v>
+        <v>-14.5528</v>
       </c>
       <c r="F33">
-        <v>10.9926</v>
+        <v>11.3472</v>
       </c>
       <c r="G33">
         <v>4.13</v>
@@ -4624,37 +4624,37 @@
         <v>1.288</v>
       </c>
       <c r="M33">
-        <v>2.20731408</v>
+        <v>2.27851776</v>
       </c>
       <c r="N33">
-        <v>-0.9193140800000004</v>
+        <v>-0.9905177600000004</v>
       </c>
       <c r="O33">
-        <v>-0.2022490976000001</v>
+        <v>-0.2179139072000001</v>
       </c>
       <c r="P33">
-        <v>-0.7170649824000003</v>
+        <v>-0.7726038528000003</v>
       </c>
       <c r="Q33">
-        <v>-0.3690649824000003</v>
+        <v>-0.4246038528000003</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1506049578473998</v>
+        <v>0.1521462072275086</v>
       </c>
       <c r="T33">
-        <v>1.365959938565035</v>
+        <v>1.386047584720403</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1283732127509466</v>
+        <v>0.1243615498524795</v>
       </c>
       <c r="W33">
-        <v>0.1750226588796099</v>
+        <v>0.1758282007896221</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5835146034133936</v>
+        <v>0.5652797720567251</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4670,22 +4670,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1597244451673849</v>
+        <v>0.1612744451673849</v>
       </c>
       <c r="C34">
-        <v>13.51528067157961</v>
+        <v>12.88239100329528</v>
       </c>
       <c r="D34">
-        <v>20.73248067157962</v>
+        <v>20.45419100329529</v>
       </c>
       <c r="E34">
-        <v>-14.5528</v>
+        <v>-14.1982</v>
       </c>
       <c r="F34">
-        <v>11.3472</v>
+        <v>11.7018</v>
       </c>
       <c r="G34">
         <v>4.13</v>
@@ -4706,37 +4706,37 @@
         <v>1.288</v>
       </c>
       <c r="M34">
-        <v>2.27851776</v>
+        <v>2.34972144</v>
       </c>
       <c r="N34">
-        <v>-0.9905177600000004</v>
+        <v>-1.06172144</v>
       </c>
       <c r="O34">
-        <v>-0.2179139072000001</v>
+        <v>-0.2335787168000001</v>
       </c>
       <c r="P34">
-        <v>-0.7726038528000003</v>
+        <v>-0.8281427232000003</v>
       </c>
       <c r="Q34">
-        <v>-0.4246038528000003</v>
+        <v>-0.4801427232000003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1521462072275086</v>
+        <v>0.1537334640517998</v>
       </c>
       <c r="T34">
-        <v>1.386047584720403</v>
+        <v>1.40673486210429</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1243615498524795</v>
+        <v>0.120593018038768</v>
       </c>
       <c r="W34">
-        <v>0.1758282007896221</v>
+        <v>0.1765849219778154</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5652797720567251</v>
+        <v>0.5481500819944001</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4752,22 +4752,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1612744451673849</v>
+        <v>0.1628244451673849</v>
       </c>
       <c r="C35">
-        <v>12.88239100329528</v>
+        <v>12.25687328170506</v>
       </c>
       <c r="D35">
-        <v>20.45419100329529</v>
+        <v>20.18327328170507</v>
       </c>
       <c r="E35">
-        <v>-14.1982</v>
+        <v>-13.8436</v>
       </c>
       <c r="F35">
-        <v>11.7018</v>
+        <v>12.0564</v>
       </c>
       <c r="G35">
         <v>4.13</v>
@@ -4788,37 +4788,37 @@
         <v>1.288</v>
       </c>
       <c r="M35">
-        <v>2.34972144</v>
+        <v>2.420925120000001</v>
       </c>
       <c r="N35">
-        <v>-1.06172144</v>
+        <v>-1.132925120000001</v>
       </c>
       <c r="O35">
-        <v>-0.2335787168000001</v>
+        <v>-0.2492435264000002</v>
       </c>
       <c r="P35">
-        <v>-0.8281427232000003</v>
+        <v>-0.8836815936000006</v>
       </c>
       <c r="Q35">
-        <v>-0.4801427232000003</v>
+        <v>-0.5356815936000007</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1537334640517998</v>
+        <v>0.1553688195677361</v>
       </c>
       <c r="T35">
-        <v>1.40673486210429</v>
+        <v>1.428049026681627</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.120593018038768</v>
+        <v>0.1170461645670395</v>
       </c>
       <c r="W35">
-        <v>0.1765849219778154</v>
+        <v>0.1772971301549385</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5481500819944001</v>
+        <v>0.5320280207592705</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4834,22 +4834,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1628244451673849</v>
+        <v>0.1643744451673849</v>
       </c>
       <c r="C36">
-        <v>12.25687328170506</v>
+        <v>11.63843840950742</v>
       </c>
       <c r="D36">
-        <v>20.18327328170507</v>
+        <v>19.91943840950742</v>
       </c>
       <c r="E36">
-        <v>-13.8436</v>
+        <v>-13.489</v>
       </c>
       <c r="F36">
-        <v>12.0564</v>
+        <v>12.411</v>
       </c>
       <c r="G36">
         <v>4.13</v>
@@ -4870,37 +4870,37 @@
         <v>1.288</v>
       </c>
       <c r="M36">
-        <v>2.420925120000001</v>
+        <v>2.4921288</v>
       </c>
       <c r="N36">
-        <v>-1.132925120000001</v>
+        <v>-1.2041288</v>
       </c>
       <c r="O36">
-        <v>-0.2492435264000002</v>
+        <v>-0.2649083360000001</v>
       </c>
       <c r="P36">
-        <v>-0.8836815936000006</v>
+        <v>-0.9392204640000003</v>
       </c>
       <c r="Q36">
-        <v>-0.5356815936000007</v>
+        <v>-0.5912204640000003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1553688195677361</v>
+        <v>0.1570544937149321</v>
       </c>
       <c r="T36">
-        <v>1.428049026681627</v>
+        <v>1.450019011707498</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1170461645670395</v>
+        <v>0.1137019884365527</v>
       </c>
       <c r="W36">
-        <v>0.1772971301549385</v>
+        <v>0.1779686407219402</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5320280207592705</v>
+        <v>0.5168272201661486</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4916,22 +4916,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1643744451673849</v>
+        <v>0.1659244451673849</v>
       </c>
       <c r="C37">
-        <v>11.63843840950742</v>
+        <v>11.02681221062081</v>
       </c>
       <c r="D37">
-        <v>19.91943840950742</v>
+        <v>19.66241221062081</v>
       </c>
       <c r="E37">
-        <v>-13.489</v>
+        <v>-13.1344</v>
       </c>
       <c r="F37">
-        <v>12.411</v>
+        <v>12.7656</v>
       </c>
       <c r="G37">
         <v>4.13</v>
@@ -4952,37 +4952,37 @@
         <v>1.288</v>
       </c>
       <c r="M37">
-        <v>2.4921288</v>
+        <v>2.56333248</v>
       </c>
       <c r="N37">
-        <v>-1.2041288</v>
+        <v>-1.27533248</v>
       </c>
       <c r="O37">
-        <v>-0.2649083360000001</v>
+        <v>-0.2805731456000001</v>
       </c>
       <c r="P37">
-        <v>-0.9392204640000003</v>
+        <v>-0.9947593344000003</v>
       </c>
       <c r="Q37">
-        <v>-0.5912204640000003</v>
+        <v>-0.6467593344000003</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1570544937149321</v>
+        <v>0.1587928451792279</v>
       </c>
       <c r="T37">
-        <v>1.450019011707498</v>
+        <v>1.472675558765428</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1137019884365527</v>
+        <v>0.1105435998688707</v>
       </c>
       <c r="W37">
-        <v>0.1779686407219402</v>
+        <v>0.1786028451463308</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5168272201661486</v>
+        <v>0.5024709084948666</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4998,22 +4998,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1659244451673849</v>
+        <v>0.180869309531279</v>
       </c>
       <c r="C38">
-        <v>11.02681221062081</v>
+        <v>8.496647053928768</v>
       </c>
       <c r="D38">
-        <v>19.66241221062081</v>
+        <v>17.48684705392877</v>
       </c>
       <c r="E38">
-        <v>-13.1344</v>
+        <v>-12.7798</v>
       </c>
       <c r="F38">
-        <v>12.7656</v>
+        <v>13.1202</v>
       </c>
       <c r="G38">
         <v>4.13</v>
@@ -5034,45 +5034,45 @@
         <v>1.288</v>
       </c>
       <c r="M38">
-        <v>2.56333248</v>
+        <v>3.09374316</v>
       </c>
       <c r="N38">
-        <v>-1.27533248</v>
+        <v>-1.80574316</v>
       </c>
       <c r="O38">
-        <v>-0.2805731456</v>
+        <v>-0.3972634952000001</v>
       </c>
       <c r="P38">
-        <v>-0.9947593343999999</v>
+        <v>-1.4084796648</v>
       </c>
       <c r="Q38">
-        <v>-0.6467593343999999</v>
+        <v>-1.0604796648</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1587928451792279</v>
+        <v>0.161292516315238</v>
       </c>
       <c r="T38">
-        <v>1.472675558765428</v>
+        <v>1.505254653318843</v>
       </c>
       <c r="U38">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.1105435998688707</v>
+        <v>0.091591313611179</v>
       </c>
       <c r="W38">
-        <v>0.1786028451463308</v>
+        <v>0.214202768250484</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.5024709084948669</v>
+        <v>0.4163241527780863</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -5080,22 +5080,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.180869309531279</v>
+        <v>0.182769309531279</v>
       </c>
       <c r="C39">
-        <v>8.496647053928768</v>
+        <v>7.899474396476064</v>
       </c>
       <c r="D39">
-        <v>17.48684705392877</v>
+        <v>17.24427439647607</v>
       </c>
       <c r="E39">
-        <v>-12.7798</v>
+        <v>-12.4252</v>
       </c>
       <c r="F39">
-        <v>13.1202</v>
+        <v>13.4748</v>
       </c>
       <c r="G39">
         <v>4.13</v>
@@ -5116,37 +5116,37 @@
         <v>1.288</v>
       </c>
       <c r="M39">
-        <v>3.09374316</v>
+        <v>3.17735784</v>
       </c>
       <c r="N39">
-        <v>-1.80574316</v>
+        <v>-1.88935784</v>
       </c>
       <c r="O39">
-        <v>-0.3972634952000001</v>
+        <v>-0.4156587248</v>
       </c>
       <c r="P39">
-        <v>-1.4084796648</v>
+        <v>-1.4736991152</v>
       </c>
       <c r="Q39">
-        <v>-1.0604796648</v>
+        <v>-1.1256991152</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.161292516315238</v>
+        <v>0.1631552988364515</v>
       </c>
       <c r="T39">
-        <v>1.505254653318843</v>
+        <v>1.529532954178825</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.091591313611179</v>
+        <v>0.08918101588456903</v>
       </c>
       <c r="W39">
-        <v>0.214202768250484</v>
+        <v>0.2147711164544186</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4163241527780863</v>
+        <v>0.4053682540207684</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5162,22 +5162,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.182769309531279</v>
+        <v>0.184669309531279</v>
       </c>
       <c r="C40">
-        <v>7.899474396476064</v>
+        <v>7.308939462660286</v>
       </c>
       <c r="D40">
-        <v>17.24427439647607</v>
+        <v>17.00833946266029</v>
       </c>
       <c r="E40">
-        <v>-12.4252</v>
+        <v>-12.0706</v>
       </c>
       <c r="F40">
-        <v>13.4748</v>
+        <v>13.8294</v>
       </c>
       <c r="G40">
         <v>4.13</v>
@@ -5198,37 +5198,37 @@
         <v>1.288</v>
       </c>
       <c r="M40">
-        <v>3.17735784</v>
+        <v>3.260972520000001</v>
       </c>
       <c r="N40">
-        <v>-1.88935784</v>
+        <v>-1.972972520000001</v>
       </c>
       <c r="O40">
-        <v>-0.4156587248</v>
+        <v>-0.4340539544000002</v>
       </c>
       <c r="P40">
-        <v>-1.4736991152</v>
+        <v>-1.538918565600001</v>
       </c>
       <c r="Q40">
-        <v>-1.1256991152</v>
+        <v>-1.190918565600001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1631552988364515</v>
+        <v>0.1650791561944261</v>
       </c>
       <c r="T40">
-        <v>1.529532954178825</v>
+        <v>1.554607264903068</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.08918101588456903</v>
+        <v>0.08689432316958007</v>
       </c>
       <c r="W40">
-        <v>0.2147711164544186</v>
+        <v>0.215310318596613</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4053682540207684</v>
+        <v>0.394974196225364</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5244,22 +5244,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.184669309531279</v>
+        <v>0.186569309531279</v>
       </c>
       <c r="C41">
-        <v>7.308939462660286</v>
+        <v>6.724773479232109</v>
       </c>
       <c r="D41">
-        <v>17.00833946266029</v>
+        <v>16.77877347923211</v>
       </c>
       <c r="E41">
-        <v>-12.0706</v>
+        <v>-11.716</v>
       </c>
       <c r="F41">
-        <v>13.8294</v>
+        <v>14.184</v>
       </c>
       <c r="G41">
         <v>4.13</v>
@@ -5280,37 +5280,37 @@
         <v>1.288</v>
       </c>
       <c r="M41">
-        <v>3.260972520000001</v>
+        <v>3.3445872</v>
       </c>
       <c r="N41">
-        <v>-1.972972520000001</v>
+        <v>-2.056587200000001</v>
       </c>
       <c r="O41">
-        <v>-0.4340539544000002</v>
+        <v>-0.4524491840000001</v>
       </c>
       <c r="P41">
-        <v>-1.538918565600001</v>
+        <v>-1.604138016</v>
       </c>
       <c r="Q41">
-        <v>-1.190918565600001</v>
+        <v>-1.256138016</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1650791561944261</v>
+        <v>0.1670671421309999</v>
       </c>
       <c r="T41">
-        <v>1.554607264903068</v>
+        <v>1.580517385984785</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08689432316958007</v>
+        <v>0.08472196509034058</v>
       </c>
       <c r="W41">
-        <v>0.215310318596613</v>
+        <v>0.2158225606316977</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.394974196225364</v>
+        <v>0.3850998413197299</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5326,22 +5326,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.186569309531279</v>
+        <v>0.188469309531279</v>
       </c>
       <c r="C42">
-        <v>6.724773479232109</v>
+        <v>6.146721990504238</v>
       </c>
       <c r="D42">
-        <v>16.77877347923211</v>
+        <v>16.55532199050424</v>
       </c>
       <c r="E42">
-        <v>-11.716</v>
+        <v>-11.3614</v>
       </c>
       <c r="F42">
-        <v>14.184</v>
+        <v>14.5386</v>
       </c>
       <c r="G42">
         <v>4.13</v>
@@ -5362,37 +5362,37 @@
         <v>1.288</v>
       </c>
       <c r="M42">
-        <v>3.3445872</v>
+        <v>3.42820188</v>
       </c>
       <c r="N42">
-        <v>-2.056587200000001</v>
+        <v>-2.140201880000001</v>
       </c>
       <c r="O42">
-        <v>-0.4524491840000001</v>
+        <v>-0.4708444136000001</v>
       </c>
       <c r="P42">
-        <v>-1.604138016</v>
+        <v>-1.669357466400001</v>
       </c>
       <c r="Q42">
-        <v>-1.256138016</v>
+        <v>-1.321357466400001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1670671421309999</v>
+        <v>0.1691225174213558</v>
       </c>
       <c r="T42">
-        <v>1.580517385984785</v>
+        <v>1.607305816255714</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08472196509034058</v>
+        <v>0.08265557569789324</v>
       </c>
       <c r="W42">
-        <v>0.2158225606316977</v>
+        <v>0.2163098152504368</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3850998413197299</v>
+        <v>0.375707162263151</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5408,22 +5408,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.188469309531279</v>
+        <v>0.190369309531279</v>
       </c>
       <c r="C43">
-        <v>6.146721990504238</v>
+        <v>5.574543917509756</v>
       </c>
       <c r="D43">
-        <v>16.55532199050424</v>
+        <v>16.33774391750976</v>
       </c>
       <c r="E43">
-        <v>-11.3614</v>
+        <v>-11.0068</v>
       </c>
       <c r="F43">
-        <v>14.5386</v>
+        <v>14.8932</v>
       </c>
       <c r="G43">
         <v>4.13</v>
@@ -5444,37 +5444,37 @@
         <v>1.288</v>
       </c>
       <c r="M43">
-        <v>3.42820188</v>
+        <v>3.511816560000001</v>
       </c>
       <c r="N43">
-        <v>-2.140201880000001</v>
+        <v>-2.223816560000001</v>
       </c>
       <c r="O43">
-        <v>-0.4708444136000001</v>
+        <v>-0.4892396432000002</v>
       </c>
       <c r="P43">
-        <v>-1.669357466400001</v>
+        <v>-1.734576916800001</v>
       </c>
       <c r="Q43">
-        <v>-1.321357466400001</v>
+        <v>-1.386576916800001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1691225174213558</v>
+        <v>0.171248767721724</v>
       </c>
       <c r="T43">
-        <v>1.607305816255714</v>
+        <v>1.635017985501502</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.08265557569789324</v>
+        <v>0.08068758580032435</v>
       </c>
       <c r="W43">
-        <v>0.2163098152504368</v>
+        <v>0.2167738672682835</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.375707162263151</v>
+        <v>0.3667617536378379</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5490,22 +5490,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.190369309531279</v>
+        <v>0.192269309531279</v>
       </c>
       <c r="C44">
-        <v>5.574543917509757</v>
+        <v>5.008010690387939</v>
       </c>
       <c r="D44">
-        <v>16.33774391750976</v>
+        <v>16.12581069038794</v>
       </c>
       <c r="E44">
-        <v>-11.0068</v>
+        <v>-10.6522</v>
       </c>
       <c r="F44">
-        <v>14.8932</v>
+        <v>15.2478</v>
       </c>
       <c r="G44">
         <v>4.13</v>
@@ -5526,37 +5526,37 @@
         <v>1.288</v>
       </c>
       <c r="M44">
-        <v>3.51181656</v>
+        <v>3.59543124</v>
       </c>
       <c r="N44">
-        <v>-2.22381656</v>
+        <v>-2.30743124</v>
       </c>
       <c r="O44">
-        <v>-0.4892396432000001</v>
+        <v>-0.5076348728000001</v>
       </c>
       <c r="P44">
-        <v>-1.7345769168</v>
+        <v>-1.7997963672</v>
       </c>
       <c r="Q44">
-        <v>-1.3865769168</v>
+        <v>-1.4517963672</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.171248767721724</v>
+        <v>0.1734496232957893</v>
       </c>
       <c r="T44">
-        <v>1.635017985501502</v>
+        <v>1.663702511562932</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08068758580032437</v>
+        <v>0.0788111303165959</v>
       </c>
       <c r="W44">
-        <v>0.2167738672682835</v>
+        <v>0.2172163354713467</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.366761753637838</v>
+        <v>0.3582324105299813</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5572,22 +5572,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.192269309531279</v>
+        <v>0.194169309531279</v>
       </c>
       <c r="C45">
-        <v>5.008010690387939</v>
+        <v>4.446905447433517</v>
       </c>
       <c r="D45">
-        <v>16.12581069038794</v>
+        <v>15.91930544743352</v>
       </c>
       <c r="E45">
-        <v>-10.6522</v>
+        <v>-10.2976</v>
       </c>
       <c r="F45">
-        <v>15.2478</v>
+        <v>15.6024</v>
       </c>
       <c r="G45">
         <v>4.13</v>
@@ -5608,37 +5608,37 @@
         <v>1.288</v>
       </c>
       <c r="M45">
-        <v>3.59543124</v>
+        <v>3.679045920000001</v>
       </c>
       <c r="N45">
-        <v>-2.30743124</v>
+        <v>-2.391045920000001</v>
       </c>
       <c r="O45">
-        <v>-0.5076348728000001</v>
+        <v>-0.5260301024000001</v>
       </c>
       <c r="P45">
-        <v>-1.7997963672</v>
+        <v>-1.865015817600001</v>
       </c>
       <c r="Q45">
-        <v>-1.4517963672</v>
+        <v>-1.517015817600001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1734496232957893</v>
+        <v>0.1757290808546427</v>
       </c>
       <c r="T45">
-        <v>1.663702511562932</v>
+        <v>1.693411484983699</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.0788111303165959</v>
+        <v>0.07701996826394597</v>
       </c>
       <c r="W45">
-        <v>0.2172163354713467</v>
+        <v>0.2176386914833615</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3582324105299813</v>
+        <v>0.3500907648361181</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5654,22 +5654,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.194169309531279</v>
+        <v>0.196069309531279</v>
       </c>
       <c r="C46">
-        <v>4.446905447433517</v>
+        <v>3.891022294909096</v>
       </c>
       <c r="D46">
-        <v>15.91930544743352</v>
+        <v>15.7180222949091</v>
       </c>
       <c r="E46">
-        <v>-10.2976</v>
+        <v>-9.942999999999998</v>
       </c>
       <c r="F46">
-        <v>15.6024</v>
+        <v>15.957</v>
       </c>
       <c r="G46">
         <v>4.13</v>
@@ -5690,37 +5690,37 @@
         <v>1.288</v>
       </c>
       <c r="M46">
-        <v>3.679045920000001</v>
+        <v>3.7626606</v>
       </c>
       <c r="N46">
-        <v>-2.391045920000001</v>
+        <v>-2.4746606</v>
       </c>
       <c r="O46">
-        <v>-0.5260301024000001</v>
+        <v>-0.5444253320000001</v>
       </c>
       <c r="P46">
-        <v>-1.865015817600001</v>
+        <v>-1.930235268</v>
       </c>
       <c r="Q46">
-        <v>-1.517015817600001</v>
+        <v>-1.582235268</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1757290808546427</v>
+        <v>0.1780914277792726</v>
       </c>
       <c r="T46">
-        <v>1.693411484983699</v>
+        <v>1.724200784710675</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07701996826394597</v>
+        <v>0.07530841341363607</v>
       </c>
       <c r="W46">
-        <v>0.2176386914833615</v>
+        <v>0.2180422761170646</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3500907648361181</v>
+        <v>0.3423109700619821</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5736,22 +5736,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.196069309531279</v>
+        <v>0.197969309531279</v>
       </c>
       <c r="C47">
-        <v>3.891022294909096</v>
+        <v>3.34016562230989</v>
       </c>
       <c r="D47">
-        <v>15.7180222949091</v>
+        <v>15.52176562230989</v>
       </c>
       <c r="E47">
-        <v>-9.942999999999998</v>
+        <v>-9.588399999999996</v>
       </c>
       <c r="F47">
-        <v>15.957</v>
+        <v>16.3116</v>
       </c>
       <c r="G47">
         <v>4.13</v>
@@ -5772,37 +5772,37 @@
         <v>1.288</v>
       </c>
       <c r="M47">
-        <v>3.7626606</v>
+        <v>3.846275280000001</v>
       </c>
       <c r="N47">
-        <v>-2.4746606</v>
+        <v>-2.558275280000001</v>
       </c>
       <c r="O47">
-        <v>-0.5444253320000001</v>
+        <v>-0.5628205616000003</v>
       </c>
       <c r="P47">
-        <v>-1.930235268</v>
+        <v>-1.995454718400001</v>
       </c>
       <c r="Q47">
-        <v>-1.582235268</v>
+        <v>-1.647454718400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1780914277792726</v>
+        <v>0.1805412690344443</v>
       </c>
       <c r="T47">
-        <v>1.724200784710675</v>
+        <v>1.756130428871984</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07530841341363607</v>
+        <v>0.07367127399160049</v>
       </c>
       <c r="W47">
-        <v>0.2180422761170646</v>
+        <v>0.2184283135927806</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3423109700619821</v>
+        <v>0.3348694272345477</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5818,22 +5818,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.197969309531279</v>
+        <v>0.199869309531279</v>
       </c>
       <c r="C48">
-        <v>3.34016562230989</v>
+        <v>2.794149468293821</v>
       </c>
       <c r="D48">
-        <v>15.52176562230989</v>
+        <v>15.33034946829382</v>
       </c>
       <c r="E48">
-        <v>-9.588399999999996</v>
+        <v>-9.233799999999999</v>
       </c>
       <c r="F48">
-        <v>16.3116</v>
+        <v>16.6662</v>
       </c>
       <c r="G48">
         <v>4.13</v>
@@ -5854,37 +5854,37 @@
         <v>1.288</v>
       </c>
       <c r="M48">
-        <v>3.846275280000001</v>
+        <v>3.92988996</v>
       </c>
       <c r="N48">
-        <v>-2.558275280000001</v>
+        <v>-2.64188996</v>
       </c>
       <c r="O48">
-        <v>-0.5628205616000003</v>
+        <v>-0.5812157912000001</v>
       </c>
       <c r="P48">
-        <v>-1.995454718400001</v>
+        <v>-2.0606741688</v>
       </c>
       <c r="Q48">
-        <v>-1.647454718400001</v>
+        <v>-1.7126741688</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1805412690344443</v>
+        <v>0.1830835571294338</v>
       </c>
       <c r="T48">
-        <v>1.756130428871984</v>
+        <v>1.789264965265795</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07367127399160049</v>
+        <v>0.0721038000768856</v>
       </c>
       <c r="W48">
-        <v>0.2184283135927806</v>
+        <v>0.2187979239418704</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3348694272345477</v>
+        <v>0.3277445458040255</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5900,22 +5900,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.199869309531279</v>
+        <v>0.201769309531279</v>
       </c>
       <c r="C49">
-        <v>2.794149468293821</v>
+        <v>2.252796932956624</v>
       </c>
       <c r="D49">
-        <v>15.33034946829382</v>
+        <v>15.14359693295663</v>
       </c>
       <c r="E49">
-        <v>-9.233799999999999</v>
+        <v>-8.879199999999997</v>
       </c>
       <c r="F49">
-        <v>16.6662</v>
+        <v>17.0208</v>
       </c>
       <c r="G49">
         <v>4.13</v>
@@ -5936,37 +5936,37 @@
         <v>1.288</v>
       </c>
       <c r="M49">
-        <v>3.92988996</v>
+        <v>4.013504640000001</v>
       </c>
       <c r="N49">
-        <v>-2.64188996</v>
+        <v>-2.725504640000001</v>
       </c>
       <c r="O49">
-        <v>-0.5812157912000001</v>
+        <v>-0.5996110208000002</v>
       </c>
       <c r="P49">
-        <v>-2.0606741688</v>
+        <v>-2.125893619200001</v>
       </c>
       <c r="Q49">
-        <v>-1.7126741688</v>
+        <v>-1.777893619200001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1830835571294338</v>
+        <v>0.1857236255357691</v>
       </c>
       <c r="T49">
-        <v>1.789264965265795</v>
+        <v>1.823673906905522</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0721038000768856</v>
+        <v>0.0706016375752838</v>
       </c>
       <c r="W49">
-        <v>0.2187979239418704</v>
+        <v>0.2191521338597481</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3277445458040255</v>
+        <v>0.3209165344331082</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5982,22 +5982,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.201769309531279</v>
+        <v>0.203669309531279</v>
       </c>
       <c r="C50">
-        <v>2.252796932956628</v>
+        <v>1.715939632547538</v>
       </c>
       <c r="D50">
-        <v>15.14359693295663</v>
+        <v>14.96133963254754</v>
       </c>
       <c r="E50">
-        <v>-8.879199999999997</v>
+        <v>-8.5246</v>
       </c>
       <c r="F50">
-        <v>17.0208</v>
+        <v>17.3754</v>
       </c>
       <c r="G50">
         <v>4.13</v>
@@ -6018,37 +6018,37 @@
         <v>1.288</v>
       </c>
       <c r="M50">
-        <v>4.013504640000001</v>
+        <v>4.09711932</v>
       </c>
       <c r="N50">
-        <v>-2.725504640000001</v>
+        <v>-2.80911932</v>
       </c>
       <c r="O50">
-        <v>-0.5996110208000002</v>
+        <v>-0.6180062504</v>
       </c>
       <c r="P50">
-        <v>-2.125893619200001</v>
+        <v>-2.1911130696</v>
       </c>
       <c r="Q50">
-        <v>-1.777893619200001</v>
+        <v>-1.8431130696</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1857236255357691</v>
+        <v>0.1884672260364705</v>
       </c>
       <c r="T50">
-        <v>1.823673906905522</v>
+        <v>1.85943221880563</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0706016375752838</v>
+        <v>0.06916078782884945</v>
       </c>
       <c r="W50">
-        <v>0.2191521338597481</v>
+        <v>0.2194918862299573</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3209165344331082</v>
+        <v>0.3143672174038612</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -6064,22 +6064,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.203669309531279</v>
+        <v>0.205569309531279</v>
       </c>
       <c r="C51">
-        <v>1.715939632547538</v>
+        <v>1.183417193092573</v>
       </c>
       <c r="D51">
-        <v>14.96133963254754</v>
+        <v>14.78341719309257</v>
       </c>
       <c r="E51">
-        <v>-8.5246</v>
+        <v>-8.169999999999998</v>
       </c>
       <c r="F51">
-        <v>17.3754</v>
+        <v>17.73</v>
       </c>
       <c r="G51">
         <v>4.13</v>
@@ -6100,37 +6100,37 @@
         <v>1.288</v>
       </c>
       <c r="M51">
-        <v>4.09711932</v>
+        <v>4.180734</v>
       </c>
       <c r="N51">
-        <v>-2.80911932</v>
+        <v>-2.892734</v>
       </c>
       <c r="O51">
-        <v>-0.6180062504</v>
+        <v>-0.6364014800000001</v>
       </c>
       <c r="P51">
-        <v>-2.1911130696</v>
+        <v>-2.25633252</v>
       </c>
       <c r="Q51">
-        <v>-1.8431130696</v>
+        <v>-1.908332520000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1884672260364705</v>
+        <v>0.1913205705571998</v>
       </c>
       <c r="T51">
-        <v>1.85943221880563</v>
+        <v>1.896620863181743</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06916078782884945</v>
+        <v>0.06777757207227246</v>
       </c>
       <c r="W51">
-        <v>0.2194918862299573</v>
+        <v>0.2198180485053582</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3143672174038612</v>
+        <v>0.3080798730557839</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6146,22 +6146,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.205569309531279</v>
+        <v>0.207469309531279</v>
       </c>
       <c r="C52">
-        <v>1.183417193092573</v>
+        <v>0.6550767797246166</v>
       </c>
       <c r="D52">
-        <v>14.78341719309257</v>
+        <v>14.60967677972462</v>
       </c>
       <c r="E52">
-        <v>-8.169999999999998</v>
+        <v>-7.815399999999997</v>
       </c>
       <c r="F52">
-        <v>17.73</v>
+        <v>18.0846</v>
       </c>
       <c r="G52">
         <v>4.13</v>
@@ -6182,37 +6182,37 @@
         <v>1.288</v>
       </c>
       <c r="M52">
-        <v>4.180734</v>
+        <v>4.26434868</v>
       </c>
       <c r="N52">
-        <v>-2.892734</v>
+        <v>-2.976348680000001</v>
       </c>
       <c r="O52">
-        <v>-0.6364014800000001</v>
+        <v>-0.6547967096000001</v>
       </c>
       <c r="P52">
-        <v>-2.25633252</v>
+        <v>-2.3215519704</v>
       </c>
       <c r="Q52">
-        <v>-1.908332520000001</v>
+        <v>-1.9735519704</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1913205705571998</v>
+        <v>0.1942903781195917</v>
       </c>
       <c r="T52">
-        <v>1.896620863181743</v>
+        <v>1.935327411409941</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06777757207227246</v>
+        <v>0.06644860007085535</v>
       </c>
       <c r="W52">
-        <v>0.2198180485053582</v>
+        <v>0.2201314201032923</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3080798730557839</v>
+        <v>0.3020390912311607</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6228,22 +6228,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.207469309531279</v>
+        <v>0.209369309531279</v>
       </c>
       <c r="C53">
-        <v>0.6550767797246166</v>
+        <v>0.1307726588169729</v>
       </c>
       <c r="D53">
-        <v>14.60967677972462</v>
+        <v>14.43997265881697</v>
       </c>
       <c r="E53">
-        <v>-7.815399999999997</v>
+        <v>-7.460799999999999</v>
       </c>
       <c r="F53">
-        <v>18.0846</v>
+        <v>18.4392</v>
       </c>
       <c r="G53">
         <v>4.13</v>
@@ -6264,37 +6264,37 @@
         <v>1.288</v>
       </c>
       <c r="M53">
-        <v>4.26434868</v>
+        <v>4.34796336</v>
       </c>
       <c r="N53">
-        <v>-2.976348680000001</v>
+        <v>-3.059963360000001</v>
       </c>
       <c r="O53">
-        <v>-0.6547967096000001</v>
+        <v>-0.6731919392000002</v>
       </c>
       <c r="P53">
-        <v>-2.3215519704</v>
+        <v>-2.386771420800001</v>
       </c>
       <c r="Q53">
-        <v>-1.9735519704</v>
+        <v>-2.038771420800001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1942903781195917</v>
+        <v>0.1973839276637499</v>
       </c>
       <c r="T53">
-        <v>1.935327411409941</v>
+        <v>1.975646732480982</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06644860007085535</v>
+        <v>0.06517074237718505</v>
       </c>
       <c r="W53">
-        <v>0.2201314201032923</v>
+        <v>0.2204327389474598</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3020390912311607</v>
+        <v>0.296230647169023</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6310,22 +6310,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.209369309531279</v>
+        <v>0.211269309531279</v>
       </c>
       <c r="C54">
-        <v>0.1307726588169729</v>
+        <v>-0.3896342097163483</v>
       </c>
       <c r="D54">
-        <v>14.43997265881697</v>
+        <v>14.27416579028365</v>
       </c>
       <c r="E54">
-        <v>-7.460799999999999</v>
+        <v>-7.106199999999998</v>
       </c>
       <c r="F54">
-        <v>18.4392</v>
+        <v>18.7938</v>
       </c>
       <c r="G54">
         <v>4.13</v>
@@ -6346,37 +6346,37 @@
         <v>1.288</v>
       </c>
       <c r="M54">
-        <v>4.34796336</v>
+        <v>4.431578040000001</v>
       </c>
       <c r="N54">
-        <v>-3.059963360000001</v>
+        <v>-3.143578040000001</v>
       </c>
       <c r="O54">
-        <v>-0.6731919392000002</v>
+        <v>-0.6915871688000002</v>
       </c>
       <c r="P54">
-        <v>-2.386771420800001</v>
+        <v>-2.4519908712</v>
       </c>
       <c r="Q54">
-        <v>-2.038771420800001</v>
+        <v>-2.103990871200001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1973839276637499</v>
+        <v>0.2006091176140424</v>
       </c>
       <c r="T54">
-        <v>1.975646732480982</v>
+        <v>2.017681769342279</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06517074237718505</v>
+        <v>0.06394110572855892</v>
       </c>
       <c r="W54">
-        <v>0.2204327389474598</v>
+        <v>0.2207226872692058</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.296230647169023</v>
+        <v>0.2906413896752679</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6392,22 +6392,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.211269309531279</v>
+        <v>0.213169309531279</v>
       </c>
       <c r="C55">
-        <v>-0.3896342097163483</v>
+        <v>-0.9062765523506862</v>
       </c>
       <c r="D55">
-        <v>14.27416579028365</v>
+        <v>14.11212344764932</v>
       </c>
       <c r="E55">
-        <v>-7.106199999999998</v>
+        <v>-6.751599999999996</v>
       </c>
       <c r="F55">
-        <v>18.7938</v>
+        <v>19.1484</v>
       </c>
       <c r="G55">
         <v>4.13</v>
@@ -6428,37 +6428,37 @@
         <v>1.288</v>
       </c>
       <c r="M55">
-        <v>4.431578040000001</v>
+        <v>4.515192720000001</v>
       </c>
       <c r="N55">
-        <v>-3.143578040000001</v>
+        <v>-3.227192720000001</v>
       </c>
       <c r="O55">
-        <v>-0.6915871688000002</v>
+        <v>-0.7099823984000002</v>
       </c>
       <c r="P55">
-        <v>-2.4519908712</v>
+        <v>-2.517210321600001</v>
       </c>
       <c r="Q55">
-        <v>-2.103990871200001</v>
+        <v>-2.169210321600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2006091176140424</v>
+        <v>0.2039745332143477</v>
       </c>
       <c r="T55">
-        <v>2.017681769342279</v>
+        <v>2.061544416501894</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06394110572855892</v>
+        <v>0.06275701117803005</v>
       </c>
       <c r="W55">
-        <v>0.2207226872692058</v>
+        <v>0.2210018967642205</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2906413896752679</v>
+        <v>0.2852591417183185</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6474,22 +6474,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.213169309531279</v>
+        <v>0.215069309531279</v>
       </c>
       <c r="C56">
-        <v>-0.9062765523506862</v>
+        <v>-1.419281136293169</v>
       </c>
       <c r="D56">
-        <v>14.11212344764932</v>
+        <v>13.95371886370684</v>
       </c>
       <c r="E56">
-        <v>-6.751599999999996</v>
+        <v>-6.396999999999995</v>
       </c>
       <c r="F56">
-        <v>19.1484</v>
+        <v>19.503</v>
       </c>
       <c r="G56">
         <v>4.13</v>
@@ -6510,37 +6510,37 @@
         <v>1.288</v>
       </c>
       <c r="M56">
-        <v>4.515192720000001</v>
+        <v>4.598807400000001</v>
       </c>
       <c r="N56">
-        <v>-3.227192720000001</v>
+        <v>-3.310807400000001</v>
       </c>
       <c r="O56">
-        <v>-0.7099823984000002</v>
+        <v>-0.7283776280000003</v>
       </c>
       <c r="P56">
-        <v>-2.517210321600001</v>
+        <v>-2.582429772000001</v>
       </c>
       <c r="Q56">
-        <v>-2.169210321600001</v>
+        <v>-2.234429772000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2039745332143477</v>
+        <v>0.2074895228413332</v>
       </c>
       <c r="T56">
-        <v>2.061544416501894</v>
+        <v>2.107356514646381</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06275701117803005</v>
+        <v>0.06161597461115677</v>
       </c>
       <c r="W56">
-        <v>0.2210018967642205</v>
+        <v>0.2212709531866892</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2852591417183185</v>
+        <v>0.2800726118688944</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6556,22 +6556,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.215069309531279</v>
+        <v>0.216969309531279</v>
       </c>
       <c r="C57">
-        <v>-1.419281136293169</v>
+        <v>-1.928769100225733</v>
       </c>
       <c r="D57">
-        <v>13.95371886370684</v>
+        <v>13.79883089977427</v>
       </c>
       <c r="E57">
-        <v>-6.396999999999995</v>
+        <v>-6.042399999999997</v>
       </c>
       <c r="F57">
-        <v>19.503</v>
+        <v>19.8576</v>
       </c>
       <c r="G57">
         <v>4.13</v>
@@ -6592,37 +6592,37 @@
         <v>1.288</v>
       </c>
       <c r="M57">
-        <v>4.598807400000001</v>
+        <v>4.68242208</v>
       </c>
       <c r="N57">
-        <v>-3.310807400000001</v>
+        <v>-3.39442208</v>
       </c>
       <c r="O57">
-        <v>-0.7283776280000003</v>
+        <v>-0.7467728576000001</v>
       </c>
       <c r="P57">
-        <v>-2.582429772000001</v>
+        <v>-2.6476492224</v>
       </c>
       <c r="Q57">
-        <v>-2.234429772000001</v>
+        <v>-2.2996492224</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2074895228413332</v>
+        <v>0.2111642847240907</v>
       </c>
       <c r="T57">
-        <v>2.107356514646381</v>
+        <v>2.155250980888344</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06161597461115677</v>
+        <v>0.06051568935024328</v>
       </c>
       <c r="W57">
-        <v>0.2212709531866892</v>
+        <v>0.2215304004512126</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2800726118688944</v>
+        <v>0.2750713152283785</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6638,22 +6638,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.216969309531279</v>
+        <v>0.218869309531279</v>
       </c>
       <c r="C58">
-        <v>-1.928769100225733</v>
+        <v>-2.434856263262187</v>
       </c>
       <c r="D58">
-        <v>13.79883089977427</v>
+        <v>13.64734373673782</v>
       </c>
       <c r="E58">
-        <v>-6.042399999999997</v>
+        <v>-5.687799999999996</v>
       </c>
       <c r="F58">
-        <v>19.8576</v>
+        <v>20.2122</v>
       </c>
       <c r="G58">
         <v>4.13</v>
@@ -6674,37 +6674,37 @@
         <v>1.288</v>
       </c>
       <c r="M58">
-        <v>4.68242208</v>
+        <v>4.76603676</v>
       </c>
       <c r="N58">
-        <v>-3.39442208</v>
+        <v>-3.478036760000001</v>
       </c>
       <c r="O58">
-        <v>-0.7467728576000001</v>
+        <v>-0.7651680872000002</v>
       </c>
       <c r="P58">
-        <v>-2.6476492224</v>
+        <v>-2.7128686728</v>
       </c>
       <c r="Q58">
-        <v>-2.2996492224</v>
+        <v>-2.364868672800001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2111642847240907</v>
+        <v>0.2150099657641859</v>
       </c>
       <c r="T58">
-        <v>2.155250980888344</v>
+        <v>2.205373096722957</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06051568935024328</v>
+        <v>0.05945401058971269</v>
       </c>
       <c r="W58">
-        <v>0.2215304004512126</v>
+        <v>0.2217807443029458</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2750713152283785</v>
+        <v>0.2702455026805122</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6720,22 +6720,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.218869309531279</v>
+        <v>0.220769309531279</v>
       </c>
       <c r="C59">
-        <v>-2.434856263262187</v>
+        <v>-2.937653413775408</v>
       </c>
       <c r="D59">
-        <v>13.64734373673782</v>
+        <v>13.4991465862246</v>
       </c>
       <c r="E59">
-        <v>-5.687799999999996</v>
+        <v>-5.333199999999994</v>
       </c>
       <c r="F59">
-        <v>20.2122</v>
+        <v>20.5668</v>
       </c>
       <c r="G59">
         <v>4.13</v>
@@ -6756,37 +6756,37 @@
         <v>1.288</v>
       </c>
       <c r="M59">
-        <v>4.76603676</v>
+        <v>4.849651440000001</v>
       </c>
       <c r="N59">
-        <v>-3.478036760000001</v>
+        <v>-3.561651440000002</v>
       </c>
       <c r="O59">
-        <v>-0.7651680872000002</v>
+        <v>-0.7835633168000004</v>
       </c>
       <c r="P59">
-        <v>-2.7128686728</v>
+        <v>-2.778088123200001</v>
       </c>
       <c r="Q59">
-        <v>-2.364868672800001</v>
+        <v>-2.430088123200001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2150099657641859</v>
+        <v>0.219038774472857</v>
       </c>
       <c r="T59">
-        <v>2.205373096722957</v>
+        <v>2.257881979978265</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05945401058971269</v>
+        <v>0.05842894144161417</v>
       </c>
       <c r="W59">
-        <v>0.2217807443029458</v>
+        <v>0.2220224556080674</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2702455026805122</v>
+        <v>0.2655860974618827</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6802,22 +6802,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.220769309531279</v>
+        <v>0.222669309531279</v>
       </c>
       <c r="C60">
-        <v>-2.937653413775408</v>
+        <v>-3.437266579608401</v>
       </c>
       <c r="D60">
-        <v>13.49914658622459</v>
+        <v>13.3541334203916</v>
       </c>
       <c r="E60">
-        <v>-5.333199999999998</v>
+        <v>-4.9786</v>
       </c>
       <c r="F60">
-        <v>20.5668</v>
+        <v>20.9214</v>
       </c>
       <c r="G60">
         <v>4.13</v>
@@ -6838,37 +6838,37 @@
         <v>1.288</v>
       </c>
       <c r="M60">
-        <v>4.849651440000001</v>
+        <v>4.93326612</v>
       </c>
       <c r="N60">
-        <v>-3.561651440000001</v>
+        <v>-3.64526612</v>
       </c>
       <c r="O60">
-        <v>-0.7835633168000001</v>
+        <v>-0.8019585464</v>
       </c>
       <c r="P60">
-        <v>-2.778088123200001</v>
+        <v>-2.8433075736</v>
       </c>
       <c r="Q60">
-        <v>-2.430088123200001</v>
+        <v>-2.4953075736</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.219038774472857</v>
+        <v>0.2232641104356096</v>
       </c>
       <c r="T60">
-        <v>2.257881979978265</v>
+        <v>2.312952272172857</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05842894144161419</v>
+        <v>0.05743862040023091</v>
       </c>
       <c r="W60">
-        <v>0.2220224556080674</v>
+        <v>0.2222559733096255</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2655860974618827</v>
+        <v>0.2610846381828678</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6884,22 +6884,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.222669309531279</v>
+        <v>0.224569309531279</v>
       </c>
       <c r="C61">
-        <v>-3.437266579608401</v>
+        <v>-3.933797281054133</v>
       </c>
       <c r="D61">
-        <v>13.3541334203916</v>
+        <v>13.21220271894587</v>
       </c>
       <c r="E61">
-        <v>-4.9786</v>
+        <v>-4.623999999999999</v>
       </c>
       <c r="F61">
-        <v>20.9214</v>
+        <v>21.276</v>
       </c>
       <c r="G61">
         <v>4.13</v>
@@ -6920,37 +6920,37 @@
         <v>1.288</v>
       </c>
       <c r="M61">
-        <v>4.93326612</v>
+        <v>5.0168808</v>
       </c>
       <c r="N61">
-        <v>-3.64526612</v>
+        <v>-3.7288808</v>
       </c>
       <c r="O61">
-        <v>-0.8019585464</v>
+        <v>-0.820353776</v>
       </c>
       <c r="P61">
-        <v>-2.8433075736</v>
+        <v>-2.908527024</v>
       </c>
       <c r="Q61">
-        <v>-2.4953075736</v>
+        <v>-2.560527024</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2232641104356096</v>
+        <v>0.2277007131964998</v>
       </c>
       <c r="T61">
-        <v>2.312952272172857</v>
+        <v>2.370776078977178</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05743862040023091</v>
+        <v>0.05648131006022706</v>
       </c>
       <c r="W61">
-        <v>0.2222559733096255</v>
+        <v>0.2224817070877985</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2610846381828678</v>
+        <v>0.2567332275464866</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6966,22 +6966,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.224569309531279</v>
+        <v>0.226469309531279</v>
       </c>
       <c r="C62">
-        <v>-3.933797281054133</v>
+        <v>-4.427342767872698</v>
       </c>
       <c r="D62">
-        <v>13.21220271894587</v>
+        <v>13.0732572321273</v>
       </c>
       <c r="E62">
-        <v>-4.623999999999999</v>
+        <v>-4.269399999999997</v>
       </c>
       <c r="F62">
-        <v>21.276</v>
+        <v>21.6306</v>
       </c>
       <c r="G62">
         <v>4.13</v>
@@ -7002,37 +7002,37 @@
         <v>1.288</v>
       </c>
       <c r="M62">
-        <v>5.0168808</v>
+        <v>5.10049548</v>
       </c>
       <c r="N62">
-        <v>-3.7288808</v>
+        <v>-3.81249548</v>
       </c>
       <c r="O62">
-        <v>-0.820353776</v>
+        <v>-0.8387490056000001</v>
       </c>
       <c r="P62">
-        <v>-2.908527024</v>
+        <v>-2.9737464744</v>
       </c>
       <c r="Q62">
-        <v>-2.560527024</v>
+        <v>-2.625746474400001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2277007131964998</v>
+        <v>0.2323648340476921</v>
       </c>
       <c r="T62">
-        <v>2.370776078977178</v>
+        <v>2.431565209207362</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05648131006022706</v>
+        <v>0.05555538694448563</v>
       </c>
       <c r="W62">
-        <v>0.2224817070877985</v>
+        <v>0.2227000397584903</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2567332275464866</v>
+        <v>0.2525244861112983</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -7048,22 +7048,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.226469309531279</v>
+        <v>0.228369309531279</v>
       </c>
       <c r="C63">
-        <v>-4.427342767872698</v>
+        <v>-4.917996241508614</v>
       </c>
       <c r="D63">
-        <v>13.0732572321273</v>
+        <v>12.93720375849138</v>
       </c>
       <c r="E63">
-        <v>-4.269399999999997</v>
+        <v>-3.9148</v>
       </c>
       <c r="F63">
-        <v>21.6306</v>
+        <v>21.9852</v>
       </c>
       <c r="G63">
         <v>4.13</v>
@@ -7084,37 +7084,37 @@
         <v>1.288</v>
       </c>
       <c r="M63">
-        <v>5.10049548</v>
+        <v>5.18411016</v>
       </c>
       <c r="N63">
-        <v>-3.81249548</v>
+        <v>-3.896110160000001</v>
       </c>
       <c r="O63">
-        <v>-0.8387490056000001</v>
+        <v>-0.8571442352000002</v>
       </c>
       <c r="P63">
-        <v>-2.9737464744</v>
+        <v>-3.0389659248</v>
       </c>
       <c r="Q63">
-        <v>-2.625746474400001</v>
+        <v>-2.6909659248</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2323648340476921</v>
+        <v>0.237274434943684</v>
       </c>
       <c r="T63">
-        <v>2.431565209207362</v>
+        <v>2.495553767344398</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05555538694448563</v>
+        <v>0.05465933231634876</v>
       </c>
       <c r="W63">
-        <v>0.2227000397584903</v>
+        <v>0.222911329439805</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2525244861112983</v>
+        <v>0.2484515105288579</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7130,22 +7130,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.228369309531279</v>
+        <v>0.230269309531279</v>
       </c>
       <c r="C64">
-        <v>-4.917996241508614</v>
+        <v>-5.405847063575393</v>
       </c>
       <c r="D64">
-        <v>12.93720375849138</v>
+        <v>12.80395293642461</v>
       </c>
       <c r="E64">
-        <v>-3.9148</v>
+        <v>-3.560199999999998</v>
       </c>
       <c r="F64">
-        <v>21.9852</v>
+        <v>22.3398</v>
       </c>
       <c r="G64">
         <v>4.13</v>
@@ -7166,37 +7166,37 @@
         <v>1.288</v>
       </c>
       <c r="M64">
-        <v>5.18411016</v>
+        <v>5.267724840000001</v>
       </c>
       <c r="N64">
-        <v>-3.896110160000001</v>
+        <v>-3.979724840000001</v>
       </c>
       <c r="O64">
-        <v>-0.8571442352000002</v>
+        <v>-0.8755394648000001</v>
       </c>
       <c r="P64">
-        <v>-3.0389659248</v>
+        <v>-3.104185375200001</v>
       </c>
       <c r="Q64">
-        <v>-2.6909659248</v>
+        <v>-2.756185375200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.237274434943684</v>
+        <v>0.2424494196718917</v>
       </c>
       <c r="T64">
-        <v>2.495553767344398</v>
+        <v>2.563001166461814</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05465933231634876</v>
+        <v>0.05379172386688291</v>
       </c>
       <c r="W64">
-        <v>0.222911329439805</v>
+        <v>0.223115911512189</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2484515105288579</v>
+        <v>0.2445078357585586</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7212,22 +7212,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.230269309531279</v>
+        <v>0.232169309531279</v>
       </c>
       <c r="C65">
-        <v>-5.405847063575393</v>
+        <v>-5.890980951587274</v>
       </c>
       <c r="D65">
-        <v>12.80395293642461</v>
+        <v>12.67341904841273</v>
       </c>
       <c r="E65">
-        <v>-3.560199999999998</v>
+        <v>-3.205599999999997</v>
       </c>
       <c r="F65">
-        <v>22.3398</v>
+        <v>22.6944</v>
       </c>
       <c r="G65">
         <v>4.13</v>
@@ -7248,37 +7248,37 @@
         <v>1.288</v>
       </c>
       <c r="M65">
-        <v>5.267724840000001</v>
+        <v>5.351339520000001</v>
       </c>
       <c r="N65">
-        <v>-3.979724840000001</v>
+        <v>-4.063339520000001</v>
       </c>
       <c r="O65">
-        <v>-0.8755394648000001</v>
+        <v>-0.8939346944000003</v>
       </c>
       <c r="P65">
-        <v>-3.104185375200001</v>
+        <v>-3.169404825600001</v>
       </c>
       <c r="Q65">
-        <v>-2.756185375200001</v>
+        <v>-2.821404825600001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2424494196718917</v>
+        <v>0.2479119035516665</v>
       </c>
       <c r="T65">
-        <v>2.563001166461814</v>
+        <v>2.634195643307976</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05379172386688291</v>
+        <v>0.05295122818146285</v>
       </c>
       <c r="W65">
-        <v>0.223115911512189</v>
+        <v>0.2233141003948111</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2445078357585586</v>
+        <v>0.2406874008248311</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7294,22 +7294,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.232169309531279</v>
+        <v>0.234069309531279</v>
       </c>
       <c r="C66">
-        <v>-5.890980951587274</v>
+        <v>-6.37348016283914</v>
       </c>
       <c r="D66">
-        <v>12.67341904841273</v>
+        <v>12.54551983716086</v>
       </c>
       <c r="E66">
-        <v>-3.205599999999997</v>
+        <v>-2.850999999999996</v>
       </c>
       <c r="F66">
-        <v>22.6944</v>
+        <v>23.049</v>
       </c>
       <c r="G66">
         <v>4.13</v>
@@ -7330,37 +7330,37 @@
         <v>1.288</v>
       </c>
       <c r="M66">
-        <v>5.351339520000001</v>
+        <v>5.434954200000001</v>
       </c>
       <c r="N66">
-        <v>-4.063339520000001</v>
+        <v>-4.146954200000001</v>
       </c>
       <c r="O66">
-        <v>-0.8939346944000003</v>
+        <v>-0.9123299240000003</v>
       </c>
       <c r="P66">
-        <v>-3.169404825600001</v>
+        <v>-3.234624276000001</v>
       </c>
       <c r="Q66">
-        <v>-2.821404825600001</v>
+        <v>-2.886624276000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2479119035516665</v>
+        <v>0.2536865293674284</v>
       </c>
       <c r="T66">
-        <v>2.634195643307976</v>
+        <v>2.709458375973918</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05295122818146285</v>
+        <v>0.05213659390174805</v>
       </c>
       <c r="W66">
-        <v>0.2233141003948111</v>
+        <v>0.2235061911579678</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2406874008248311</v>
+        <v>0.2369845177352183</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7376,22 +7376,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.234069309531279</v>
+        <v>0.235969309531279</v>
       </c>
       <c r="C67">
-        <v>-6.37348016283914</v>
+        <v>-6.853423667263471</v>
       </c>
       <c r="D67">
-        <v>12.54551983716086</v>
+        <v>12.42017633273653</v>
       </c>
       <c r="E67">
-        <v>-2.850999999999996</v>
+        <v>-2.496399999999998</v>
       </c>
       <c r="F67">
-        <v>23.049</v>
+        <v>23.4036</v>
       </c>
       <c r="G67">
         <v>4.13</v>
@@ -7412,37 +7412,37 @@
         <v>1.288</v>
       </c>
       <c r="M67">
-        <v>5.434954200000001</v>
+        <v>5.51856888</v>
       </c>
       <c r="N67">
-        <v>-4.146954200000001</v>
+        <v>-4.23056888</v>
       </c>
       <c r="O67">
-        <v>-0.9123299240000003</v>
+        <v>-0.9307251536</v>
       </c>
       <c r="P67">
-        <v>-3.234624276000001</v>
+        <v>-3.2998437264</v>
       </c>
       <c r="Q67">
-        <v>-2.886624276000001</v>
+        <v>-2.9518437264</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2536865293674284</v>
+        <v>0.2598008390547057</v>
       </c>
       <c r="T67">
-        <v>2.709458375973918</v>
+        <v>2.789148328208445</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05213659390174805</v>
+        <v>0.05134664550929732</v>
       </c>
       <c r="W67">
-        <v>0.2235061911579678</v>
+        <v>0.2236924609889077</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2369845177352183</v>
+        <v>0.2333938432240789</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7458,22 +7458,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.235969309531279</v>
+        <v>0.237869309531279</v>
       </c>
       <c r="C68">
-        <v>-6.853423667263471</v>
+        <v>-7.330887310027578</v>
       </c>
       <c r="D68">
-        <v>12.42017633273653</v>
+        <v>12.29731268997243</v>
       </c>
       <c r="E68">
-        <v>-2.496399999999998</v>
+        <v>-2.141799999999996</v>
       </c>
       <c r="F68">
-        <v>23.4036</v>
+        <v>23.7582</v>
       </c>
       <c r="G68">
         <v>4.13</v>
@@ -7494,37 +7494,37 @@
         <v>1.288</v>
       </c>
       <c r="M68">
-        <v>5.51856888</v>
+        <v>5.602183560000001</v>
       </c>
       <c r="N68">
-        <v>-4.23056888</v>
+        <v>-4.314183560000002</v>
       </c>
       <c r="O68">
-        <v>-0.9307251536</v>
+        <v>-0.9491203832000004</v>
       </c>
       <c r="P68">
-        <v>-3.2998437264</v>
+        <v>-3.365063176800001</v>
       </c>
       <c r="Q68">
-        <v>-2.9518437264</v>
+        <v>-3.017063176800002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2598008390547057</v>
+        <v>0.2662857129654543</v>
       </c>
       <c r="T68">
-        <v>2.789148328208445</v>
+        <v>2.873667974517792</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05134664550929732</v>
+        <v>0.05058027766587496</v>
       </c>
       <c r="W68">
-        <v>0.2236924609889077</v>
+        <v>0.2238731705263867</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2333938432240789</v>
+        <v>0.2299103530267043</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7540,22 +7540,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.237869309531279</v>
+        <v>0.239769309531279</v>
       </c>
       <c r="C69">
-        <v>-7.330887310027578</v>
+        <v>-7.80594396457467</v>
       </c>
       <c r="D69">
-        <v>12.29731268997243</v>
+        <v>12.17685603542533</v>
       </c>
       <c r="E69">
-        <v>-2.141799999999996</v>
+        <v>-1.787199999999995</v>
       </c>
       <c r="F69">
-        <v>23.7582</v>
+        <v>24.1128</v>
       </c>
       <c r="G69">
         <v>4.13</v>
@@ -7576,37 +7576,37 @@
         <v>1.288</v>
       </c>
       <c r="M69">
-        <v>5.602183560000001</v>
+        <v>5.685798240000001</v>
       </c>
       <c r="N69">
-        <v>-4.314183560000002</v>
+        <v>-4.397798240000002</v>
       </c>
       <c r="O69">
-        <v>-0.9491203832000004</v>
+        <v>-0.9675156128000004</v>
       </c>
       <c r="P69">
-        <v>-3.365063176800001</v>
+        <v>-3.430282627200001</v>
       </c>
       <c r="Q69">
-        <v>-3.017063176800002</v>
+        <v>-3.082282627200001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2662857129654543</v>
+        <v>0.2731758914956248</v>
       </c>
       <c r="T69">
-        <v>2.873667974517792</v>
+        <v>2.963470098721473</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05058027766587496</v>
+        <v>0.04983645005314151</v>
       </c>
       <c r="W69">
-        <v>0.2238731705263867</v>
+        <v>0.2240485650774692</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2299103530267043</v>
+        <v>0.2265293184233704</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7622,22 +7622,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.239769309531279</v>
+        <v>0.241669309531279</v>
       </c>
       <c r="C70">
-        <v>-7.80594396457467</v>
+        <v>-8.278663676757617</v>
       </c>
       <c r="D70">
-        <v>12.17685603542533</v>
+        <v>12.05873632324238</v>
       </c>
       <c r="E70">
-        <v>-1.787199999999995</v>
+        <v>-1.432599999999997</v>
       </c>
       <c r="F70">
-        <v>24.1128</v>
+        <v>24.4674</v>
       </c>
       <c r="G70">
         <v>4.13</v>
@@ -7658,37 +7658,37 @@
         <v>1.288</v>
       </c>
       <c r="M70">
-        <v>5.685798240000001</v>
+        <v>5.769412920000001</v>
       </c>
       <c r="N70">
-        <v>-4.397798240000002</v>
+        <v>-4.48141292</v>
       </c>
       <c r="O70">
-        <v>-0.9675156128000004</v>
+        <v>-0.9859108424</v>
       </c>
       <c r="P70">
-        <v>-3.430282627200001</v>
+        <v>-3.4955020776</v>
       </c>
       <c r="Q70">
-        <v>-3.082282627200001</v>
+        <v>-3.1475020776</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2731758914956248</v>
+        <v>0.280510597672903</v>
       </c>
       <c r="T70">
-        <v>2.963470098721473</v>
+        <v>3.059065908357649</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04983645005314151</v>
+        <v>0.049114182661067</v>
       </c>
       <c r="W70">
-        <v>0.2240485650774692</v>
+        <v>0.2242188757285204</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2265293184233704</v>
+        <v>0.2232462848230319</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7704,22 +7704,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.241669309531279</v>
+        <v>0.243569309531279</v>
       </c>
       <c r="C71">
-        <v>-8.278663676757617</v>
+        <v>-8.749113800664418</v>
       </c>
       <c r="D71">
-        <v>12.05873632324238</v>
+        <v>11.94288619933558</v>
       </c>
       <c r="E71">
-        <v>-1.432599999999997</v>
+        <v>-1.077999999999996</v>
       </c>
       <c r="F71">
-        <v>24.4674</v>
+        <v>24.822</v>
       </c>
       <c r="G71">
         <v>4.13</v>
@@ -7740,37 +7740,37 @@
         <v>1.288</v>
       </c>
       <c r="M71">
-        <v>5.769412920000001</v>
+        <v>5.853027600000001</v>
       </c>
       <c r="N71">
-        <v>-4.48141292</v>
+        <v>-4.565027600000001</v>
       </c>
       <c r="O71">
-        <v>-0.9859108424</v>
+        <v>-1.004306072</v>
       </c>
       <c r="P71">
-        <v>-3.4955020776</v>
+        <v>-3.560721528</v>
       </c>
       <c r="Q71">
-        <v>-3.1475020776</v>
+        <v>-3.212721528</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.280510597672903</v>
+        <v>0.2883342842619998</v>
       </c>
       <c r="T71">
-        <v>3.059065908357649</v>
+        <v>3.161034771969571</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.049114182661067</v>
+        <v>0.04841255148019461</v>
       </c>
       <c r="W71">
-        <v>0.2242188757285204</v>
+        <v>0.2243843203609701</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2232462848230319</v>
+        <v>0.2200570521827029</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7786,22 +7786,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.243569309531279</v>
+        <v>0.245469309531279</v>
       </c>
       <c r="C72">
-        <v>-8.749113800664418</v>
+        <v>-9.217359126688766</v>
       </c>
       <c r="D72">
-        <v>11.94288619933558</v>
+        <v>11.82924087331124</v>
       </c>
       <c r="E72">
-        <v>-1.077999999999996</v>
+        <v>-0.7233999999999945</v>
       </c>
       <c r="F72">
-        <v>24.822</v>
+        <v>25.1766</v>
       </c>
       <c r="G72">
         <v>4.13</v>
@@ -7822,37 +7822,37 @@
         <v>1.288</v>
       </c>
       <c r="M72">
-        <v>5.853027600000001</v>
+        <v>5.936642280000001</v>
       </c>
       <c r="N72">
-        <v>-4.565027600000001</v>
+        <v>-4.648642280000001</v>
       </c>
       <c r="O72">
-        <v>-1.004306072</v>
+        <v>-1.0227013016</v>
       </c>
       <c r="P72">
-        <v>-3.560721528</v>
+        <v>-3.625940978400001</v>
       </c>
       <c r="Q72">
-        <v>-3.212721528</v>
+        <v>-3.277940978400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2883342842619998</v>
+        <v>0.2966975354434481</v>
       </c>
       <c r="T72">
-        <v>3.161034771969571</v>
+        <v>3.270035971003006</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04841255148019461</v>
+        <v>0.04773068455793835</v>
       </c>
       <c r="W72">
-        <v>0.2243843203609701</v>
+        <v>0.2245451045812381</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2200570521827029</v>
+        <v>0.216957657081538</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7868,22 +7868,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.245469309531279</v>
+        <v>0.247369309531279</v>
       </c>
       <c r="C73">
-        <v>-9.217359126688759</v>
+        <v>-9.683462002357455</v>
       </c>
       <c r="D73">
-        <v>11.82924087331124</v>
+        <v>11.71773799764254</v>
       </c>
       <c r="E73">
-        <v>-0.723399999999998</v>
+        <v>-0.3688000000000002</v>
       </c>
       <c r="F73">
-        <v>25.1766</v>
+        <v>25.5312</v>
       </c>
       <c r="G73">
         <v>4.13</v>
@@ -7904,37 +7904,37 @@
         <v>1.288</v>
       </c>
       <c r="M73">
-        <v>5.93664228</v>
+        <v>6.02025696</v>
       </c>
       <c r="N73">
-        <v>-4.648642280000001</v>
+        <v>-4.732256960000001</v>
       </c>
       <c r="O73">
-        <v>-1.0227013016</v>
+        <v>-1.0410965312</v>
       </c>
       <c r="P73">
-        <v>-3.625940978400001</v>
+        <v>-3.691160428800001</v>
       </c>
       <c r="Q73">
-        <v>-3.277940978400001</v>
+        <v>-3.343160428800001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.296697535443448</v>
+        <v>0.3056581617092854</v>
       </c>
       <c r="T73">
-        <v>3.270035971003004</v>
+        <v>3.386822969967397</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04773068455793836</v>
+        <v>0.04706775838352255</v>
       </c>
       <c r="W73">
-        <v>0.2245451045812381</v>
+        <v>0.2247014225731654</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2169576570815379</v>
+        <v>0.2139443562887388</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7950,22 +7950,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.247369309531279</v>
+        <v>0.249269309531279</v>
       </c>
       <c r="C74">
-        <v>-9.683462002357455</v>
+        <v>-10.1474824463881</v>
       </c>
       <c r="D74">
-        <v>11.71773799764254</v>
+        <v>11.6083175536119</v>
       </c>
       <c r="E74">
-        <v>-0.3688000000000002</v>
+        <v>-0.01419999999999888</v>
       </c>
       <c r="F74">
-        <v>25.5312</v>
+        <v>25.8858</v>
       </c>
       <c r="G74">
         <v>4.13</v>
@@ -7986,37 +7986,37 @@
         <v>1.288</v>
       </c>
       <c r="M74">
-        <v>6.02025696</v>
+        <v>6.10387164</v>
       </c>
       <c r="N74">
-        <v>-4.732256960000001</v>
+        <v>-4.815871640000001</v>
       </c>
       <c r="O74">
-        <v>-1.0410965312</v>
+        <v>-1.0594917608</v>
       </c>
       <c r="P74">
-        <v>-3.691160428800001</v>
+        <v>-3.756379879200001</v>
       </c>
       <c r="Q74">
-        <v>-3.343160428800001</v>
+        <v>-3.408379879200001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3056581617092854</v>
+        <v>0.3152825380688886</v>
       </c>
       <c r="T74">
-        <v>3.386822969967397</v>
+        <v>3.512260857743967</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04706775838352255</v>
+        <v>0.04642299457004963</v>
       </c>
       <c r="W74">
-        <v>0.2247014225731654</v>
+        <v>0.2248534578803823</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2139443562887388</v>
+        <v>0.2110136116820437</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -8032,22 +8032,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.249269309531279</v>
+        <v>0.251169309531279</v>
       </c>
       <c r="C75">
-        <v>-10.1474824463881</v>
+        <v>-10.60947825641542</v>
       </c>
       <c r="D75">
-        <v>11.6083175536119</v>
+        <v>11.50092174358458</v>
       </c>
       <c r="E75">
-        <v>-0.01419999999999888</v>
+        <v>0.3404000000000025</v>
       </c>
       <c r="F75">
-        <v>25.8858</v>
+        <v>26.2404</v>
       </c>
       <c r="G75">
         <v>4.13</v>
@@ -8068,37 +8068,37 @@
         <v>1.288</v>
       </c>
       <c r="M75">
-        <v>6.10387164</v>
+        <v>6.187486320000001</v>
       </c>
       <c r="N75">
-        <v>-4.815871640000001</v>
+        <v>-4.899486320000001</v>
       </c>
       <c r="O75">
-        <v>-1.0594917608</v>
+        <v>-1.0778869904</v>
       </c>
       <c r="P75">
-        <v>-3.756379879200001</v>
+        <v>-3.821599329600001</v>
       </c>
       <c r="Q75">
-        <v>-3.408379879200001</v>
+        <v>-3.473599329600001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3152825380688886</v>
+        <v>0.3256472510715381</v>
       </c>
       <c r="T75">
-        <v>3.512260857743967</v>
+        <v>3.647347813811043</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04642299457004963</v>
+        <v>0.0457956568055895</v>
       </c>
       <c r="W75">
-        <v>0.2248534578803823</v>
+        <v>0.225001384125242</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2110136116820437</v>
+        <v>0.2081620763890432</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8114,22 +8114,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.251169309531279</v>
+        <v>0.253069309531279</v>
       </c>
       <c r="C76">
-        <v>-10.60947825641542</v>
+        <v>-11.06950511079258</v>
       </c>
       <c r="D76">
-        <v>11.50092174358458</v>
+        <v>11.39549488920741</v>
       </c>
       <c r="E76">
-        <v>0.3404000000000025</v>
+        <v>0.6950000000000003</v>
       </c>
       <c r="F76">
-        <v>26.2404</v>
+        <v>26.595</v>
       </c>
       <c r="G76">
         <v>4.13</v>
@@ -8150,37 +8150,37 @@
         <v>1.288</v>
       </c>
       <c r="M76">
-        <v>6.187486320000001</v>
+        <v>6.271101</v>
       </c>
       <c r="N76">
-        <v>-4.899486320000001</v>
+        <v>-4.983101</v>
       </c>
       <c r="O76">
-        <v>-1.0778869904</v>
+        <v>-1.09628222</v>
       </c>
       <c r="P76">
-        <v>-3.821599329600001</v>
+        <v>-3.88681878</v>
       </c>
       <c r="Q76">
-        <v>-3.473599329600001</v>
+        <v>-3.53881878</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3256472510715381</v>
+        <v>0.3368411411143997</v>
       </c>
       <c r="T76">
-        <v>3.647347813811043</v>
+        <v>3.793241726363485</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0457956568055895</v>
+        <v>0.04518504804818164</v>
       </c>
       <c r="W76">
-        <v>0.225001384125242</v>
+        <v>0.2251453656702388</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2081620763890432</v>
+        <v>0.2053865820371894</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8196,22 +8196,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.253069309531279</v>
+        <v>0.2549693095312791</v>
       </c>
       <c r="C77">
-        <v>-11.06950511079258</v>
+        <v>-11.52761666484424</v>
       </c>
       <c r="D77">
-        <v>11.39549488920741</v>
+        <v>11.29198333515576</v>
       </c>
       <c r="E77">
-        <v>0.6950000000000003</v>
+        <v>1.049600000000002</v>
       </c>
       <c r="F77">
-        <v>26.595</v>
+        <v>26.9496</v>
       </c>
       <c r="G77">
         <v>4.13</v>
@@ -8232,37 +8232,37 @@
         <v>1.288</v>
       </c>
       <c r="M77">
-        <v>6.271101</v>
+        <v>6.35471568</v>
       </c>
       <c r="N77">
-        <v>-4.983101</v>
+        <v>-5.06671568</v>
       </c>
       <c r="O77">
-        <v>-1.09628222</v>
+        <v>-1.1146774496</v>
       </c>
       <c r="P77">
-        <v>-3.88681878</v>
+        <v>-3.952038230399999</v>
       </c>
       <c r="Q77">
-        <v>-3.53881878</v>
+        <v>-3.6040382304</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3368411411143997</v>
+        <v>0.3489678553274997</v>
       </c>
       <c r="T77">
-        <v>3.793241726363485</v>
+        <v>3.951293464961964</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04518504804818164</v>
+        <v>0.04459050794228452</v>
       </c>
       <c r="W77">
-        <v>0.2251453656702388</v>
+        <v>0.2252855582272093</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2053865820371894</v>
+        <v>0.2026841270103843</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8278,22 +8278,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2549693095312791</v>
+        <v>0.256869309531279</v>
       </c>
       <c r="C78">
-        <v>-11.52761666484424</v>
+        <v>-11.98386464192078</v>
       </c>
       <c r="D78">
-        <v>11.29198333515576</v>
+        <v>11.19033535807922</v>
       </c>
       <c r="E78">
-        <v>1.049600000000002</v>
+        <v>1.404200000000003</v>
       </c>
       <c r="F78">
-        <v>26.9496</v>
+        <v>27.3042</v>
       </c>
       <c r="G78">
         <v>4.13</v>
@@ -8314,37 +8314,37 @@
         <v>1.288</v>
       </c>
       <c r="M78">
-        <v>6.35471568</v>
+        <v>6.438330360000001</v>
       </c>
       <c r="N78">
-        <v>-5.06671568</v>
+        <v>-5.150330360000002</v>
       </c>
       <c r="O78">
-        <v>-1.1146774496</v>
+        <v>-1.1330726792</v>
       </c>
       <c r="P78">
-        <v>-3.952038230399999</v>
+        <v>-4.017257680800001</v>
       </c>
       <c r="Q78">
-        <v>-3.6040382304</v>
+        <v>-3.669257680800001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3489678553274997</v>
+        <v>0.3621490664286954</v>
       </c>
       <c r="T78">
-        <v>3.951293464961964</v>
+        <v>4.123088833003789</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04459050794228452</v>
+        <v>0.04401141043654055</v>
       </c>
       <c r="W78">
-        <v>0.2252855582272093</v>
+        <v>0.2254221094190637</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2026841270103843</v>
+        <v>0.2000518656206388</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8360,22 +8360,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.256869309531279</v>
+        <v>0.258769309531279</v>
       </c>
       <c r="C79">
-        <v>-11.98386464192078</v>
+        <v>-12.43829891957865</v>
       </c>
       <c r="D79">
-        <v>11.19033535807922</v>
+        <v>11.09050108042135</v>
       </c>
       <c r="E79">
-        <v>1.404200000000003</v>
+        <v>1.758800000000004</v>
       </c>
       <c r="F79">
-        <v>27.3042</v>
+        <v>27.6588</v>
       </c>
       <c r="G79">
         <v>4.13</v>
@@ -8396,37 +8396,37 @@
         <v>1.288</v>
       </c>
       <c r="M79">
-        <v>6.438330360000001</v>
+        <v>6.521945040000001</v>
       </c>
       <c r="N79">
-        <v>-5.150330360000002</v>
+        <v>-5.233945040000002</v>
       </c>
       <c r="O79">
-        <v>-1.1330726792</v>
+        <v>-1.1514679088</v>
       </c>
       <c r="P79">
-        <v>-4.017257680800001</v>
+        <v>-4.082477131200001</v>
       </c>
       <c r="Q79">
-        <v>-3.669257680800001</v>
+        <v>-3.734477131200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3621490664286954</v>
+        <v>0.3765285694481815</v>
       </c>
       <c r="T79">
-        <v>4.123088833003789</v>
+        <v>4.310501961776688</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04401141043654055</v>
+        <v>0.04344716158479003</v>
       </c>
       <c r="W79">
-        <v>0.2254221094190637</v>
+        <v>0.2255551592983065</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2000518656206388</v>
+        <v>0.1974870981126819</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8442,22 +8442,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.258769309531279</v>
+        <v>0.260669309531279</v>
       </c>
       <c r="C80">
-        <v>-12.43829891957865</v>
+        <v>-12.89096761118829</v>
       </c>
       <c r="D80">
-        <v>11.09050108042135</v>
+        <v>10.99243238881171</v>
       </c>
       <c r="E80">
-        <v>1.758800000000004</v>
+        <v>2.113400000000002</v>
       </c>
       <c r="F80">
-        <v>27.6588</v>
+        <v>28.0134</v>
       </c>
       <c r="G80">
         <v>4.13</v>
@@ -8478,37 +8478,37 @@
         <v>1.288</v>
       </c>
       <c r="M80">
-        <v>6.521945040000001</v>
+        <v>6.60555972</v>
       </c>
       <c r="N80">
-        <v>-5.233945040000002</v>
+        <v>-5.31755972</v>
       </c>
       <c r="O80">
-        <v>-1.1514679088</v>
+        <v>-1.1698631384</v>
       </c>
       <c r="P80">
-        <v>-4.082477131200001</v>
+        <v>-4.1476965816</v>
       </c>
       <c r="Q80">
-        <v>-3.734477131200001</v>
+        <v>-3.7996965816</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3765285694481815</v>
+        <v>0.392277548945714</v>
       </c>
       <c r="T80">
-        <v>4.310501961776688</v>
+        <v>4.515763959956531</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04344716158479003</v>
+        <v>0.04289719751409649</v>
       </c>
       <c r="W80">
-        <v>0.2255551592983065</v>
+        <v>0.2256848408261761</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1974870981126819</v>
+        <v>0.1949872614277114</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8524,22 +8524,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.260669309531279</v>
+        <v>0.262569309531279</v>
       </c>
       <c r="C81">
-        <v>-12.89096761118829</v>
+        <v>-13.3419171432503</v>
       </c>
       <c r="D81">
-        <v>10.99243238881171</v>
+        <v>10.8960828567497</v>
       </c>
       <c r="E81">
-        <v>2.113400000000002</v>
+        <v>2.468000000000004</v>
       </c>
       <c r="F81">
-        <v>28.0134</v>
+        <v>28.368</v>
       </c>
       <c r="G81">
         <v>4.13</v>
@@ -8560,37 +8560,37 @@
         <v>1.288</v>
       </c>
       <c r="M81">
-        <v>6.60555972</v>
+        <v>6.689174400000001</v>
       </c>
       <c r="N81">
-        <v>-5.31755972</v>
+        <v>-5.4011744</v>
       </c>
       <c r="O81">
-        <v>-1.1698631384</v>
+        <v>-1.188258368</v>
       </c>
       <c r="P81">
-        <v>-4.1476965816</v>
+        <v>-4.212916032000001</v>
       </c>
       <c r="Q81">
-        <v>-3.7996965816</v>
+        <v>-3.864916032000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.392277548945714</v>
+        <v>0.4096014263929997</v>
       </c>
       <c r="T81">
-        <v>4.515763959956531</v>
+        <v>4.741552157954358</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04289719751409649</v>
+        <v>0.04236098254517029</v>
       </c>
       <c r="W81">
-        <v>0.2256848408261761</v>
+        <v>0.2258112803158489</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1949872614277114</v>
+        <v>0.192549920659865</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8606,22 +8606,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.262569309531279</v>
+        <v>0.264469309531279</v>
       </c>
       <c r="C82">
-        <v>-13.3419171432503</v>
+        <v>-13.79119232868076</v>
       </c>
       <c r="D82">
-        <v>10.8960828567497</v>
+        <v>10.80140767131924</v>
       </c>
       <c r="E82">
-        <v>2.468000000000004</v>
+        <v>2.822600000000005</v>
       </c>
       <c r="F82">
-        <v>28.368</v>
+        <v>28.7226</v>
       </c>
       <c r="G82">
         <v>4.13</v>
@@ -8642,37 +8642,37 @@
         <v>1.288</v>
       </c>
       <c r="M82">
-        <v>6.689174400000001</v>
+        <v>6.772789080000001</v>
       </c>
       <c r="N82">
-        <v>-5.4011744</v>
+        <v>-5.484789080000001</v>
       </c>
       <c r="O82">
-        <v>-1.188258368</v>
+        <v>-1.2066535976</v>
       </c>
       <c r="P82">
-        <v>-4.212916032000001</v>
+        <v>-4.278135482400001</v>
       </c>
       <c r="Q82">
-        <v>-3.864916032000001</v>
+        <v>-3.930135482400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4096014263929997</v>
+        <v>0.428748869887368</v>
       </c>
       <c r="T82">
-        <v>4.741552157954358</v>
+        <v>4.991107534688797</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04236098254517029</v>
+        <v>0.04183800745202004</v>
       </c>
       <c r="W82">
-        <v>0.2258112803158489</v>
+        <v>0.2259345978428137</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.192549920659865</v>
+        <v>0.1901727611455457</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8688,22 +8688,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.264469309531279</v>
+        <v>0.266369309531279</v>
       </c>
       <c r="C83">
-        <v>-13.79119232868076</v>
+        <v>-14.23883643630896</v>
       </c>
       <c r="D83">
-        <v>10.80140767131924</v>
+        <v>10.70836356369104</v>
       </c>
       <c r="E83">
-        <v>2.822600000000005</v>
+        <v>3.177200000000003</v>
       </c>
       <c r="F83">
-        <v>28.7226</v>
+        <v>29.0772</v>
       </c>
       <c r="G83">
         <v>4.13</v>
@@ -8724,37 +8724,37 @@
         <v>1.288</v>
       </c>
       <c r="M83">
-        <v>6.772789080000001</v>
+        <v>6.856403760000001</v>
       </c>
       <c r="N83">
-        <v>-5.484789080000001</v>
+        <v>-5.568403760000001</v>
       </c>
       <c r="O83">
-        <v>-1.2066535976</v>
+        <v>-1.2250488272</v>
       </c>
       <c r="P83">
-        <v>-4.278135482400001</v>
+        <v>-4.343354932800001</v>
       </c>
       <c r="Q83">
-        <v>-3.930135482400001</v>
+        <v>-3.995354932800001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.428748869887368</v>
+        <v>0.450023807103333</v>
       </c>
       <c r="T83">
-        <v>4.991107534688797</v>
+        <v>5.268391286615953</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04183800745202004</v>
+        <v>0.04132778784894662</v>
       </c>
       <c r="W83">
-        <v>0.2259345978428137</v>
+        <v>0.2260549076252184</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1901727611455457</v>
+        <v>0.1878535811315756</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8770,22 +8770,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.266369309531279</v>
+        <v>0.268269309531279</v>
       </c>
       <c r="C84">
-        <v>-14.23883643630896</v>
+        <v>-14.68489125681377</v>
       </c>
       <c r="D84">
-        <v>10.70836356369104</v>
+        <v>10.61690874318623</v>
       </c>
       <c r="E84">
-        <v>3.177200000000003</v>
+        <v>3.531800000000004</v>
       </c>
       <c r="F84">
-        <v>29.0772</v>
+        <v>29.4318</v>
       </c>
       <c r="G84">
         <v>4.13</v>
@@ -8806,37 +8806,37 @@
         <v>1.288</v>
       </c>
       <c r="M84">
-        <v>6.856403760000001</v>
+        <v>6.940018440000001</v>
       </c>
       <c r="N84">
-        <v>-5.568403760000001</v>
+        <v>-5.652018440000001</v>
       </c>
       <c r="O84">
-        <v>-1.2250488272</v>
+        <v>-1.2434440568</v>
       </c>
       <c r="P84">
-        <v>-4.343354932800001</v>
+        <v>-4.4085743832</v>
       </c>
       <c r="Q84">
-        <v>-3.995354932800001</v>
+        <v>-4.060574383200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.450023807103333</v>
+        <v>0.4738016781094115</v>
       </c>
       <c r="T84">
-        <v>5.268391286615953</v>
+        <v>5.578296656416892</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04132778784894662</v>
+        <v>0.04082986269414004</v>
       </c>
       <c r="W84">
-        <v>0.2260549076252184</v>
+        <v>0.2261723183767218</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1878535811315756</v>
+        <v>0.1855902849733638</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8852,22 +8852,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.268269309531279</v>
+        <v>0.270169309531279</v>
       </c>
       <c r="C85">
-        <v>-14.68489125681377</v>
+        <v>-15.12939716530988</v>
       </c>
       <c r="D85">
-        <v>10.61690874318623</v>
+        <v>10.52700283469012</v>
       </c>
       <c r="E85">
-        <v>3.531800000000004</v>
+        <v>3.886400000000005</v>
       </c>
       <c r="F85">
-        <v>29.4318</v>
+        <v>29.7864</v>
       </c>
       <c r="G85">
         <v>4.13</v>
@@ -8888,37 +8888,37 @@
         <v>1.288</v>
       </c>
       <c r="M85">
-        <v>6.940018440000001</v>
+        <v>7.023633120000001</v>
       </c>
       <c r="N85">
-        <v>-5.652018440000001</v>
+        <v>-5.735633120000001</v>
       </c>
       <c r="O85">
-        <v>-1.2434440568</v>
+        <v>-1.2618392864</v>
       </c>
       <c r="P85">
-        <v>-4.4085743832</v>
+        <v>-4.4737938336</v>
       </c>
       <c r="Q85">
-        <v>-4.060574383200001</v>
+        <v>-4.1257938336</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4738016781094115</v>
+        <v>0.5005517829912497</v>
       </c>
       <c r="T85">
-        <v>5.578296656416892</v>
+        <v>5.926940197442948</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04082986269414004</v>
+        <v>0.04034379290016218</v>
       </c>
       <c r="W85">
-        <v>0.2261723183767218</v>
+        <v>0.2262869336341418</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1855902849733638</v>
+        <v>0.183380876818919</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8934,22 +8934,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.270169309531279</v>
+        <v>0.272069309531279</v>
       </c>
       <c r="C86">
-        <v>-15.12939716530988</v>
+        <v>-15.57239318078075</v>
       </c>
       <c r="D86">
-        <v>10.52700283469012</v>
+        <v>10.43860681921925</v>
       </c>
       <c r="E86">
-        <v>3.886400000000002</v>
+        <v>4.241</v>
       </c>
       <c r="F86">
-        <v>29.7864</v>
+        <v>30.141</v>
       </c>
       <c r="G86">
         <v>4.13</v>
@@ -8970,37 +8970,37 @@
         <v>1.288</v>
       </c>
       <c r="M86">
-        <v>7.02363312</v>
+        <v>7.1072478</v>
       </c>
       <c r="N86">
-        <v>-5.735633120000001</v>
+        <v>-5.819247799999999</v>
       </c>
       <c r="O86">
-        <v>-1.2618392864</v>
+        <v>-1.280234516</v>
       </c>
       <c r="P86">
-        <v>-4.4737938336</v>
+        <v>-4.539013283999999</v>
       </c>
       <c r="Q86">
-        <v>-4.1257938336</v>
+        <v>-4.191013283999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5005517829912495</v>
+        <v>0.5308685685239994</v>
       </c>
       <c r="T86">
-        <v>5.926940197442945</v>
+        <v>6.322069543939142</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04034379290016218</v>
+        <v>0.03986916004251322</v>
       </c>
       <c r="W86">
-        <v>0.2262869336341418</v>
+        <v>0.2263988520619754</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1833808768189189</v>
+        <v>0.1812234547386965</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -9016,22 +9016,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.272069309531279</v>
+        <v>0.273969309531279</v>
       </c>
       <c r="C87">
-        <v>-15.57239318078075</v>
+        <v>-16.0139170225422</v>
       </c>
       <c r="D87">
-        <v>10.43860681921925</v>
+        <v>10.3516829774578</v>
       </c>
       <c r="E87">
-        <v>4.241</v>
+        <v>4.595600000000001</v>
       </c>
       <c r="F87">
-        <v>30.141</v>
+        <v>30.4956</v>
       </c>
       <c r="G87">
         <v>4.13</v>
@@ -9052,37 +9052,37 @@
         <v>1.288</v>
       </c>
       <c r="M87">
-        <v>7.1072478</v>
+        <v>7.19086248</v>
       </c>
       <c r="N87">
-        <v>-5.819247799999999</v>
+        <v>-5.90286248</v>
       </c>
       <c r="O87">
-        <v>-1.280234516</v>
+        <v>-1.2986297456</v>
       </c>
       <c r="P87">
-        <v>-4.539013283999999</v>
+        <v>-4.6042327344</v>
       </c>
       <c r="Q87">
-        <v>-4.191013283999999</v>
+        <v>-4.2562327344</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5308685685239994</v>
+        <v>0.5655163234185707</v>
       </c>
       <c r="T87">
-        <v>6.322069543939142</v>
+        <v>6.773645939934794</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03986916004251322</v>
+        <v>0.03940556515829795</v>
       </c>
       <c r="W87">
-        <v>0.2263988520619754</v>
+        <v>0.2265081677356733</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1812234547386965</v>
+        <v>0.1791162052649907</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -9098,22 +9098,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.273969309531279</v>
+        <v>0.275869309531279</v>
       </c>
       <c r="C88">
-        <v>-16.0139170225422</v>
+        <v>-16.45400516390812</v>
       </c>
       <c r="D88">
-        <v>10.3516829774578</v>
+        <v>10.26619483609188</v>
       </c>
       <c r="E88">
-        <v>4.595600000000001</v>
+        <v>4.950200000000002</v>
       </c>
       <c r="F88">
-        <v>30.4956</v>
+        <v>30.8502</v>
       </c>
       <c r="G88">
         <v>4.13</v>
@@ -9134,37 +9134,37 @@
         <v>1.288</v>
       </c>
       <c r="M88">
-        <v>7.19086248</v>
+        <v>7.274477160000001</v>
       </c>
       <c r="N88">
-        <v>-5.90286248</v>
+        <v>-5.986477160000002</v>
       </c>
       <c r="O88">
-        <v>-1.2986297456</v>
+        <v>-1.3170249752</v>
       </c>
       <c r="P88">
-        <v>-4.6042327344</v>
+        <v>-4.669452184800001</v>
       </c>
       <c r="Q88">
-        <v>-4.2562327344</v>
+        <v>-4.321452184800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5655163234185707</v>
+        <v>0.6054945021430762</v>
       </c>
       <c r="T88">
-        <v>6.773645939934794</v>
+        <v>7.294695627622086</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03940556515829795</v>
+        <v>0.03895262762774279</v>
       </c>
       <c r="W88">
-        <v>0.2265081677356733</v>
+        <v>0.2266149704053783</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1791162052649907</v>
+        <v>0.1770573983079218</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9180,22 +9180,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.275869309531279</v>
+        <v>0.277769309531279</v>
       </c>
       <c r="C89">
-        <v>-16.45400516390812</v>
+        <v>-16.89269288321888</v>
       </c>
       <c r="D89">
-        <v>10.26619483609188</v>
+        <v>10.18210711678112</v>
       </c>
       <c r="E89">
-        <v>4.950200000000002</v>
+        <v>5.304800000000004</v>
       </c>
       <c r="F89">
-        <v>30.8502</v>
+        <v>31.2048</v>
       </c>
       <c r="G89">
         <v>4.13</v>
@@ -9216,37 +9216,37 @@
         <v>1.288</v>
       </c>
       <c r="M89">
-        <v>7.274477160000001</v>
+        <v>7.358091840000001</v>
       </c>
       <c r="N89">
-        <v>-5.986477160000002</v>
+        <v>-6.070091840000002</v>
       </c>
       <c r="O89">
-        <v>-1.3170249752</v>
+        <v>-1.3354202048</v>
       </c>
       <c r="P89">
-        <v>-4.669452184800001</v>
+        <v>-4.734671635200002</v>
       </c>
       <c r="Q89">
-        <v>-4.321452184800001</v>
+        <v>-4.386671635200002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6054945021430762</v>
+        <v>0.6521357106549994</v>
       </c>
       <c r="T89">
-        <v>7.294695627622086</v>
+        <v>7.902586929923928</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03895262762774279</v>
+        <v>0.03850998413197299</v>
       </c>
       <c r="W89">
-        <v>0.2266149704053783</v>
+        <v>0.2267193457416808</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1770573983079218</v>
+        <v>0.175045382418059</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9262,22 +9262,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.277769309531279</v>
+        <v>0.279669309531279</v>
       </c>
       <c r="C90">
-        <v>-16.89269288321888</v>
+        <v>-17.33001431238227</v>
       </c>
       <c r="D90">
-        <v>10.18210711678112</v>
+        <v>10.09938568761773</v>
       </c>
       <c r="E90">
-        <v>5.304800000000004</v>
+        <v>5.659400000000002</v>
       </c>
       <c r="F90">
-        <v>31.2048</v>
+        <v>31.5594</v>
       </c>
       <c r="G90">
         <v>4.13</v>
@@ -9298,37 +9298,37 @@
         <v>1.288</v>
       </c>
       <c r="M90">
-        <v>7.358091840000001</v>
+        <v>7.44170652</v>
       </c>
       <c r="N90">
-        <v>-6.070091840000002</v>
+        <v>-6.15370652</v>
       </c>
       <c r="O90">
-        <v>-1.3354202048</v>
+        <v>-1.3538154344</v>
       </c>
       <c r="P90">
-        <v>-4.734671635200002</v>
+        <v>-4.799891085600001</v>
       </c>
       <c r="Q90">
-        <v>-4.386671635200002</v>
+        <v>-4.451891085600001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6521357106549994</v>
+        <v>0.7072571388963629</v>
       </c>
       <c r="T90">
-        <v>7.902586929923928</v>
+        <v>8.621003923553376</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03850998413197299</v>
+        <v>0.03807728768105195</v>
       </c>
       <c r="W90">
-        <v>0.2267193457416808</v>
+        <v>0.226821375564808</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.175045382418059</v>
+        <v>0.1730785803684179</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9344,22 +9344,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.279669309531279</v>
+        <v>0.281569309531279</v>
       </c>
       <c r="C91">
-        <v>-17.33001431238227</v>
+        <v>-17.76600248306752</v>
       </c>
       <c r="D91">
-        <v>10.09938568761773</v>
+        <v>10.01799751693248</v>
       </c>
       <c r="E91">
-        <v>5.659400000000002</v>
+        <v>6.014000000000003</v>
       </c>
       <c r="F91">
-        <v>31.5594</v>
+        <v>31.914</v>
       </c>
       <c r="G91">
         <v>4.13</v>
@@ -9380,37 +9380,37 @@
         <v>1.288</v>
       </c>
       <c r="M91">
-        <v>7.44170652</v>
+        <v>7.5253212</v>
       </c>
       <c r="N91">
-        <v>-6.15370652</v>
+        <v>-6.2373212</v>
       </c>
       <c r="O91">
-        <v>-1.3538154344</v>
+        <v>-1.372210664</v>
       </c>
       <c r="P91">
-        <v>-4.799891085600001</v>
+        <v>-4.865110536</v>
       </c>
       <c r="Q91">
-        <v>-4.451891085600001</v>
+        <v>-4.517110536000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7072571388963629</v>
+        <v>0.7734028527859993</v>
       </c>
       <c r="T91">
-        <v>8.621003923553376</v>
+        <v>9.483104315908715</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03807728768105195</v>
+        <v>0.03765420670681804</v>
       </c>
       <c r="W91">
-        <v>0.226821375564808</v>
+        <v>0.2269211380585323</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1730785803684179</v>
+        <v>0.1711554850309911</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9426,22 +9426,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.281569309531279</v>
+        <v>0.283469309531279</v>
       </c>
       <c r="C92">
-        <v>-17.76600248306752</v>
+        <v>-18.20068937068338</v>
       </c>
       <c r="D92">
-        <v>10.01799751693248</v>
+        <v>9.937910629316621</v>
       </c>
       <c r="E92">
-        <v>6.014000000000003</v>
+        <v>6.368600000000001</v>
       </c>
       <c r="F92">
-        <v>31.914</v>
+        <v>32.2686</v>
       </c>
       <c r="G92">
         <v>4.13</v>
@@ -9462,37 +9462,37 @@
         <v>1.288</v>
       </c>
       <c r="M92">
-        <v>7.5253212</v>
+        <v>7.60893588</v>
       </c>
       <c r="N92">
-        <v>-6.2373212</v>
+        <v>-6.32093588</v>
       </c>
       <c r="O92">
-        <v>-1.372210664</v>
+        <v>-1.3906058936</v>
       </c>
       <c r="P92">
-        <v>-4.865110536</v>
+        <v>-4.9303299864</v>
       </c>
       <c r="Q92">
-        <v>-4.517110536000001</v>
+        <v>-4.5823299864</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7734028527859993</v>
+        <v>0.8542476142066658</v>
       </c>
       <c r="T92">
-        <v>9.483104315908715</v>
+        <v>10.53678257323191</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03765420670681804</v>
+        <v>0.03724042421553433</v>
       </c>
       <c r="W92">
-        <v>0.2269211380585323</v>
+        <v>0.227018707969977</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1711554850309911</v>
+        <v>0.169274655525156</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9508,22 +9508,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.283469309531279</v>
+        <v>0.285369309531279</v>
       </c>
       <c r="C93">
-        <v>-18.20068937068338</v>
+        <v>-18.63410593626369</v>
       </c>
       <c r="D93">
-        <v>9.937910629316621</v>
+        <v>9.859094063736311</v>
       </c>
       <c r="E93">
-        <v>6.368600000000001</v>
+        <v>6.723200000000006</v>
       </c>
       <c r="F93">
-        <v>32.2686</v>
+        <v>32.6232</v>
       </c>
       <c r="G93">
         <v>4.13</v>
@@ -9544,37 +9544,37 @@
         <v>1.288</v>
       </c>
       <c r="M93">
-        <v>7.60893588</v>
+        <v>7.692550560000002</v>
       </c>
       <c r="N93">
-        <v>-6.32093588</v>
+        <v>-6.404550560000002</v>
       </c>
       <c r="O93">
-        <v>-1.3906058936</v>
+        <v>-1.409001123200001</v>
       </c>
       <c r="P93">
-        <v>-4.9303299864</v>
+        <v>-4.995549436800002</v>
       </c>
       <c r="Q93">
-        <v>-4.5823299864</v>
+        <v>-4.647549436800002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8542476142066658</v>
+        <v>0.9553035659824994</v>
       </c>
       <c r="T93">
-        <v>10.53678257323191</v>
+        <v>11.8538803948859</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03724042421553433</v>
+        <v>0.03683563699580025</v>
       </c>
       <c r="W93">
-        <v>0.227018707969977</v>
+        <v>0.2271141567963903</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.169274655525156</v>
+        <v>0.1674347136172738</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9590,22 +9590,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.285369309531279</v>
+        <v>0.287269309531279</v>
       </c>
       <c r="C94">
-        <v>-18.63410593626369</v>
+        <v>-19.06628216637534</v>
       </c>
       <c r="D94">
-        <v>9.859094063736311</v>
+        <v>9.78151783362466</v>
       </c>
       <c r="E94">
-        <v>6.723200000000006</v>
+        <v>7.077800000000003</v>
       </c>
       <c r="F94">
-        <v>32.6232</v>
+        <v>32.9778</v>
       </c>
       <c r="G94">
         <v>4.13</v>
@@ -9626,37 +9626,37 @@
         <v>1.288</v>
       </c>
       <c r="M94">
-        <v>7.692550560000002</v>
+        <v>7.776165240000001</v>
       </c>
       <c r="N94">
-        <v>-6.404550560000002</v>
+        <v>-6.488165240000001</v>
       </c>
       <c r="O94">
-        <v>-1.409001123200001</v>
+        <v>-1.4273963528</v>
       </c>
       <c r="P94">
-        <v>-4.995549436800002</v>
+        <v>-5.0607688872</v>
       </c>
       <c r="Q94">
-        <v>-4.647549436800002</v>
+        <v>-4.7127688872</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9553035659824994</v>
+        <v>1.085232646837142</v>
       </c>
       <c r="T94">
-        <v>11.8538803948859</v>
+        <v>13.5472918798696</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03683563699580025</v>
+        <v>0.03643955487756584</v>
       </c>
       <c r="W94">
-        <v>0.2271141567963903</v>
+        <v>0.22720755295987</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1674347136172738</v>
+        <v>0.1656343403525721</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9672,22 +9672,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.287269309531279</v>
+        <v>0.289169309531279</v>
       </c>
       <c r="C95">
-        <v>-19.06628216637534</v>
+        <v>-19.49724711115691</v>
       </c>
       <c r="D95">
-        <v>9.78151783362466</v>
+        <v>9.705152888843086</v>
       </c>
       <c r="E95">
-        <v>7.077800000000003</v>
+        <v>7.432400000000001</v>
       </c>
       <c r="F95">
-        <v>32.9778</v>
+        <v>33.3324</v>
       </c>
       <c r="G95">
         <v>4.13</v>
@@ -9708,37 +9708,37 @@
         <v>1.288</v>
       </c>
       <c r="M95">
-        <v>7.776165240000001</v>
+        <v>7.85977992</v>
       </c>
       <c r="N95">
-        <v>-6.488165240000001</v>
+        <v>-6.571779920000001</v>
       </c>
       <c r="O95">
-        <v>-1.4273963528</v>
+        <v>-1.4457915824</v>
       </c>
       <c r="P95">
-        <v>-5.0607688872</v>
+        <v>-5.125988337600001</v>
       </c>
       <c r="Q95">
-        <v>-4.7127688872</v>
+        <v>-4.777988337600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.085232646837142</v>
+        <v>1.25847142131</v>
       </c>
       <c r="T95">
-        <v>13.5472918798696</v>
+        <v>15.80517385984787</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03643955487756584</v>
+        <v>0.0360519000384428</v>
       </c>
       <c r="W95">
-        <v>0.22720755295987</v>
+        <v>0.2272989619709352</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1656343403525721</v>
+        <v>0.1638722729020127</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9754,22 +9754,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.289169309531279</v>
+        <v>0.291069309531279</v>
       </c>
       <c r="C96">
-        <v>-19.49724711115691</v>
+        <v>-19.92702892058934</v>
       </c>
       <c r="D96">
-        <v>9.705152888843086</v>
+        <v>9.629971079410662</v>
       </c>
       <c r="E96">
-        <v>7.432400000000001</v>
+        <v>7.787000000000006</v>
       </c>
       <c r="F96">
-        <v>33.3324</v>
+        <v>33.687</v>
       </c>
       <c r="G96">
         <v>4.13</v>
@@ -9790,37 +9790,37 @@
         <v>1.288</v>
       </c>
       <c r="M96">
-        <v>7.85977992</v>
+        <v>7.943394600000001</v>
       </c>
       <c r="N96">
-        <v>-6.571779920000001</v>
+        <v>-6.655394600000001</v>
       </c>
       <c r="O96">
-        <v>-1.4457915824</v>
+        <v>-1.464186812</v>
       </c>
       <c r="P96">
-        <v>-5.125988337600001</v>
+        <v>-5.191207788000001</v>
       </c>
       <c r="Q96">
-        <v>-4.777988337600001</v>
+        <v>-4.843207788000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.25847142131</v>
+        <v>1.501005705572001</v>
       </c>
       <c r="T96">
-        <v>15.80517385984787</v>
+        <v>18.96620863181745</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0360519000384428</v>
+        <v>0.03567240635382761</v>
       </c>
       <c r="W96">
-        <v>0.2272989619709352</v>
+        <v>0.2273884465817675</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1638722729020127</v>
+        <v>0.1621473016083074</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9836,22 +9836,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.291069309531279</v>
+        <v>0.292969309531279</v>
       </c>
       <c r="C97">
-        <v>-19.92702892058934</v>
+        <v>-20.35565487909356</v>
       </c>
       <c r="D97">
-        <v>9.629971079410662</v>
+        <v>9.555945120906438</v>
       </c>
       <c r="E97">
-        <v>7.787000000000006</v>
+        <v>8.141600000000004</v>
       </c>
       <c r="F97">
-        <v>33.687</v>
+        <v>34.0416</v>
       </c>
       <c r="G97">
         <v>4.13</v>
@@ -9872,37 +9872,37 @@
         <v>1.288</v>
       </c>
       <c r="M97">
-        <v>7.943394600000001</v>
+        <v>8.027009280000001</v>
       </c>
       <c r="N97">
-        <v>-6.655394600000001</v>
+        <v>-6.739009280000001</v>
       </c>
       <c r="O97">
-        <v>-1.464186812</v>
+        <v>-1.4825820416</v>
       </c>
       <c r="P97">
-        <v>-5.191207788000001</v>
+        <v>-5.256427238400001</v>
       </c>
       <c r="Q97">
-        <v>-4.843207788000001</v>
+        <v>-4.908427238400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.501005705572001</v>
+        <v>1.864807131965001</v>
       </c>
       <c r="T97">
-        <v>18.96620863181745</v>
+        <v>23.70776078977183</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03567240635382761</v>
+        <v>0.0353008187876419</v>
       </c>
       <c r="W97">
-        <v>0.2273884465817675</v>
+        <v>0.227476066929874</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1621473016083074</v>
+        <v>0.1604582672165542</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9918,22 +9918,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.292969309531279</v>
+        <v>0.294869309531279</v>
       </c>
       <c r="C98">
-        <v>-20.35565487909356</v>
+        <v>-20.78315143854478</v>
       </c>
       <c r="D98">
-        <v>9.555945120906442</v>
+        <v>9.483048561455215</v>
       </c>
       <c r="E98">
-        <v>8.141600000000004</v>
+        <v>8.496200000000002</v>
       </c>
       <c r="F98">
-        <v>34.0416</v>
+        <v>34.3962</v>
       </c>
       <c r="G98">
         <v>4.13</v>
@@ -9954,37 +9954,37 @@
         <v>1.288</v>
       </c>
       <c r="M98">
-        <v>8.027009280000001</v>
+        <v>8.11062396</v>
       </c>
       <c r="N98">
-        <v>-6.739009280000001</v>
+        <v>-6.82262396</v>
       </c>
       <c r="O98">
-        <v>-1.4825820416</v>
+        <v>-1.5009772712</v>
       </c>
       <c r="P98">
-        <v>-5.256427238400001</v>
+        <v>-5.3216466888</v>
       </c>
       <c r="Q98">
-        <v>-4.908427238400001</v>
+        <v>-4.9736466888</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.864807131964997</v>
+        <v>2.471142842619996</v>
       </c>
       <c r="T98">
-        <v>23.70776078977176</v>
+        <v>31.61034771969569</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0353008187876419</v>
+        <v>0.03493689282075901</v>
       </c>
       <c r="W98">
-        <v>0.227476066929874</v>
+        <v>0.227561880672865</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1604582672165542</v>
+        <v>0.1588040582761774</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -10000,22 +10000,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.294869309531279</v>
+        <v>0.296769309531279</v>
       </c>
       <c r="C99">
-        <v>-20.78315143854478</v>
+        <v>-21.20954424978698</v>
       </c>
       <c r="D99">
-        <v>9.483048561455215</v>
+        <v>9.411255750213014</v>
       </c>
       <c r="E99">
-        <v>8.496200000000002</v>
+        <v>8.8508</v>
       </c>
       <c r="F99">
-        <v>34.3962</v>
+        <v>34.7508</v>
       </c>
       <c r="G99">
         <v>4.13</v>
@@ -10036,37 +10036,37 @@
         <v>1.288</v>
       </c>
       <c r="M99">
-        <v>8.11062396</v>
+        <v>8.19423864</v>
       </c>
       <c r="N99">
-        <v>-6.82262396</v>
+        <v>-6.90623864</v>
       </c>
       <c r="O99">
-        <v>-1.5009772712</v>
+        <v>-1.5193725008</v>
       </c>
       <c r="P99">
-        <v>-5.3216466888</v>
+        <v>-5.3868661392</v>
       </c>
       <c r="Q99">
-        <v>-4.9736466888</v>
+        <v>-5.0388661392</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.471142842619996</v>
+        <v>3.683814263929993</v>
       </c>
       <c r="T99">
-        <v>31.61034771969569</v>
+        <v>47.41552157954352</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03493689282075901</v>
+        <v>0.03458039391442472</v>
       </c>
       <c r="W99">
-        <v>0.227561880672865</v>
+        <v>0.2276459431149787</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1588040582761774</v>
+        <v>0.1571836087019306</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -10082,22 +10082,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.296769309531279</v>
+        <v>0.298669309531279</v>
       </c>
       <c r="C100">
-        <v>-21.20954424978698</v>
+        <v>-21.63485819272672</v>
       </c>
       <c r="D100">
-        <v>9.411255750213014</v>
+        <v>9.340541807273279</v>
       </c>
       <c r="E100">
-        <v>8.8508</v>
+        <v>9.205400000000004</v>
       </c>
       <c r="F100">
-        <v>34.7508</v>
+        <v>35.1054</v>
       </c>
       <c r="G100">
         <v>4.13</v>
@@ -10118,37 +10118,37 @@
         <v>1.288</v>
       </c>
       <c r="M100">
-        <v>8.19423864</v>
+        <v>8.27785332</v>
       </c>
       <c r="N100">
-        <v>-6.90623864</v>
+        <v>-6.98985332</v>
       </c>
       <c r="O100">
-        <v>-1.5193725008</v>
+        <v>-1.5377677304</v>
       </c>
       <c r="P100">
-        <v>-5.3868661392</v>
+        <v>-5.4520855896</v>
       </c>
       <c r="Q100">
-        <v>-5.0388661392</v>
+        <v>-5.1040855896</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.683814263929993</v>
+        <v>7.321828527859986</v>
       </c>
       <c r="T100">
-        <v>47.41552157954352</v>
+        <v>94.83104315908705</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03458039391442472</v>
+        <v>0.03423109700619822</v>
       </c>
       <c r="W100">
-        <v>0.2276459431149787</v>
+        <v>0.2277283073259385</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10156,91 +10156,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1571836087019306</v>
+        <v>0.1555958954827192</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.298669309531279</v>
-      </c>
-      <c r="C101">
-        <v>-21.63485819272672</v>
-      </c>
-      <c r="D101">
-        <v>9.340541807273279</v>
-      </c>
-      <c r="E101">
-        <v>9.205400000000004</v>
-      </c>
-      <c r="F101">
-        <v>35.1054</v>
-      </c>
-      <c r="G101">
-        <v>4.13</v>
-      </c>
-      <c r="H101">
-        <v>9.56</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.636</v>
-      </c>
-      <c r="K101">
-        <v>0.348</v>
-      </c>
-      <c r="L101">
-        <v>1.288</v>
-      </c>
-      <c r="M101">
-        <v>8.27785332</v>
-      </c>
-      <c r="N101">
-        <v>-6.98985332</v>
-      </c>
-      <c r="O101">
-        <v>-1.5377677304</v>
-      </c>
-      <c r="P101">
-        <v>-5.4520855896</v>
-      </c>
-      <c r="Q101">
-        <v>-5.1040855896</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.321828527859986</v>
-      </c>
-      <c r="T101">
-        <v>94.83104315908705</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03423109700619822</v>
-      </c>
-      <c r="W101">
-        <v>0.2277283073259385</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1555958954827192</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
